--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B8" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B93" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Handle</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Blue Island</v>
+        <v>petal</v>
       </c>
       <c r="G102" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H102" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L102" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>From Down Here</v>
+        <v>Come Inside</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>From Down Here - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G103" t="str">
-        <v>4:01</v>
+        <v>3:13</v>
       </c>
       <c r="H103" t="str">
-        <v>Lola Young</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L103" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>the cure</v>
+        <v>Game Time</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>4:57</v>
+        <v>3:26</v>
       </c>
       <c r="H104" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Future</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L104" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SS26</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>SS26 - Single</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:47</v>
+        <v>2:36</v>
       </c>
       <c r="H105" t="str">
-        <v>Charli xcx</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L105" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>White Flag</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Cry Baby</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G106" t="str">
-        <v>2:34</v>
+        <v>3:22</v>
       </c>
       <c r="H106" t="str">
-        <v>Vince Staples</v>
+        <v>Young Miko</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L106" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Knew Better Part Two</v>
+        <v>Handle</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>Blue Island</v>
       </c>
       <c r="G107" t="str">
-        <v>2:44</v>
+        <v>3:06</v>
       </c>
       <c r="H107" t="str">
-        <v>Ariana Grande</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L107" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Goals</v>
+        <v>The Wave</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H108" t="str">
-        <v>LISA</v>
+        <v>Jungle</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L108" t="str">
-        <v>Goals - LISA</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>The Wave</v>
+        <v>STOP</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sunshine</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:22</v>
+        <v>2:56</v>
       </c>
       <c r="H109" t="str">
-        <v>Jungle</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L109" t="str">
-        <v>The Wave - Jungle</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>we should talk</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G110" t="str">
-        <v>3:04</v>
+        <v>3:08</v>
       </c>
       <c r="H110" t="str">
-        <v>Bleachers</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L110" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>The Thread</v>
       </c>
       <c r="G111" t="str">
-        <v>3:26</v>
+        <v>3:27</v>
       </c>
       <c r="H111" t="str">
-        <v>The Band CAMINO</v>
+        <v>WILLOW</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L111" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>STOP</v>
+        <v>No Fear</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G112" t="str">
-        <v>2:56</v>
+        <v>3:38</v>
       </c>
       <c r="H112" t="str">
-        <v>Bella Kay</v>
+        <v>Iceage</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L112" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Ego</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Ego - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G113" t="str">
-        <v>2:53</v>
+        <v>3:11</v>
       </c>
       <c r="H113" t="str">
-        <v>The Warning</v>
+        <v>Latto</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L113" t="str">
-        <v>Ego - The Warning</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:17</v>
+        <v>2:48</v>
       </c>
       <c r="H114" t="str">
-        <v>Kylie Minogue</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L114" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>All That Matters</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:43</v>
+        <v>3:35</v>
       </c>
       <c r="H115" t="str">
-        <v>6LACK</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L115" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Like A Virgin</v>
+        <v>Rubio</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Terrified .</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G116" t="str">
-        <v>2:34</v>
+        <v>4:42</v>
       </c>
       <c r="H116" t="str">
-        <v>fakemink</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L116" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>24 Hours</v>
+        <v>Pary</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>24 Hours - Single</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>2:52</v>
       </c>
       <c r="H117" t="str">
-        <v>Stormzy</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L117" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G118" t="str">
-        <v>2:09</v>
+        <v>3:48</v>
       </c>
       <c r="H118" t="str">
-        <v>Lizzo</v>
+        <v>Riley Green</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L118" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Ms. Tundra</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Highway 79</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H119" t="str">
-        <v>Ne-Yo</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L119" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>TARENTINO</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:23</v>
+        <v>2:47</v>
       </c>
       <c r="H120" t="str">
-        <v>Labrinth</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L120" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Daydreamin’</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:58</v>
+        <v>4:49</v>
       </c>
       <c r="H121" t="str">
-        <v>ZAYN</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L121" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>End of an Era</v>
+        <v>minute</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Dinner Party</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>3:38</v>
+        <v>2:59</v>
       </c>
       <c r="H122" t="str">
-        <v>Niall Horan</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L122" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Questions</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Florescence</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>3:07</v>
+        <v>2:48</v>
       </c>
       <c r="H123" t="str">
-        <v>Maisie Peters</v>
+        <v>Labrinth</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L123" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Thug</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Blondshell</v>
+        <v>G Herbo</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L124" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>Clap</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:44</v>
+        <v>2:04</v>
       </c>
       <c r="H125" t="str">
-        <v>Kygo</v>
+        <v>Polo G</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L125" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>OMAKASE</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G126" t="str">
-        <v>4:03</v>
+        <v>2:47</v>
       </c>
       <c r="H126" t="str">
-        <v>Álvaro Díaz</v>
+        <v>YG</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L126" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Dosis</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>DOSIS</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G127" t="str">
-        <v>3:00</v>
+        <v>2:50</v>
       </c>
       <c r="H127" t="str">
-        <v>Xavi</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L127" t="str">
-        <v>Dosis - Xavi</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G128" t="str">
-        <v>2:36</v>
+        <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Diplo</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L128" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Saving This Bottle</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:05</v>
+        <v>3:37</v>
       </c>
       <c r="H129" t="str">
-        <v>Diplo</v>
+        <v>Santana</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L129" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>The Climb</v>
+        <v>london</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>The Climb - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:50</v>
+        <v>3:23</v>
       </c>
       <c r="H130" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L130" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>everything tatted</v>
+        <v>Caution</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>everything tatted - Single</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G131" t="str">
-        <v>3:25</v>
+        <v>2:43</v>
       </c>
       <c r="H131" t="str">
-        <v>mgk</v>
+        <v>NMIXX</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L131" t="str">
-        <v>everything tatted - mgk</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>BOOMPALA</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G132" t="str">
-        <v>2:56</v>
+        <v>3:07</v>
       </c>
       <c r="H132" t="str">
-        <v>LE SSERAFIM</v>
+        <v>aespa</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L132" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>can we do it all again?</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G133" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H133" t="str">
-        <v>Sonny Fodera</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L133" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:28</v>
+        <v>2:42</v>
       </c>
       <c r="H134" t="str">
-        <v>Sheff G</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L134" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>touch myself</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>and all pride aside</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G135" t="str">
-        <v>4:09</v>
+        <v>3:06</v>
       </c>
       <c r="H135" t="str">
-        <v>kwn</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L135" t="str">
-        <v>touch myself - kwn</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Comes and Goes</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G136" t="str">
-        <v>4:22</v>
+        <v>2:48</v>
       </c>
       <c r="H136" t="str">
-        <v>KETTAMA</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L136" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Dear God</v>
+        <v>Coil</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Dear God</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G137" t="str">
-        <v>6:08</v>
+        <v>3:54</v>
       </c>
       <c r="H137" t="str">
-        <v>The Pretty Reckless</v>
+        <v>ear</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L137" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Hexagons</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>The Wow! Signal</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>5:26</v>
+        <v>3:30</v>
       </c>
       <c r="H138" t="str">
-        <v>Muse</v>
+        <v>Kneecap</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L138" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Facile-Batiste</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Black Mozart</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>4:55</v>
+        <v>3:04</v>
       </c>
       <c r="H139" t="str">
-        <v>Jon Batiste</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L139" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Pop Pop</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Pop Pop - Single</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:57</v>
+        <v>3:18</v>
       </c>
       <c r="H140" t="str">
-        <v>Channel Tres</v>
+        <v>Perrie</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L140" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>One Of Us</v>
+        <v>Man of the House</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>One Of Us - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G141" t="str">
-        <v>3:35</v>
+        <v>2:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Chris Young</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L141" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Sins of the Father</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:20</v>
+        <v>2:37</v>
       </c>
       <c r="H142" t="str">
-        <v>Moses Sumney</v>
+        <v>MEEK</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L142" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Life On The Run</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Life On The Run - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:49</v>
+        <v>4:34</v>
       </c>
       <c r="H143" t="str">
-        <v>Brandi Carlile</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L143" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>New York Confident</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>New York Confident - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:27</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Mark Ambor</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L144" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>pequeñita!</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>pequeñita! - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:39</v>
+        <v>1:45</v>
       </c>
       <c r="H145" t="str">
-        <v>Judeline</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L145" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Opaline</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:17</v>
+        <v>4:15</v>
       </c>
       <c r="H146" t="str">
-        <v>Stephan Moccio</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L146" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Pretty Little Things</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:51</v>
+        <v>3:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Lauv</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L147" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>COLORADO</v>
+        <v>12 Steps</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>COLORADO - Single</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>1:54</v>
+        <v>3:11</v>
       </c>
       <c r="H148" t="str">
-        <v>Loud Luxury</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L148" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Infidelidad</v>
+        <v>Over And Over</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>El Disco de Salsa</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G149" t="str">
-        <v>3:29</v>
+        <v>4:38</v>
       </c>
       <c r="H149" t="str">
-        <v>Neutro Shorty</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L149" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Y'all Won</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G150" t="str">
-        <v>2:57</v>
+        <v>2:22</v>
       </c>
       <c r="H150" t="str">
-        <v>Veeze</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L150" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>La Semana</v>
+        <v>Mad About It</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:30</v>
+        <v>2:37</v>
       </c>
       <c r="H151" t="str">
-        <v>ELENA ROSE</v>
+        <v>Dasha</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L151" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Bandera Blanca</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:34</v>
+        <v>2:59</v>
       </c>
       <c r="H152" t="str">
-        <v>Christian Nodal</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L152" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Cold</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Cold - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H153" t="str">
-        <v>Majid Jordan</v>
+        <v>Knox</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L153" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>blue jeans</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:15</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Ecca Vandal</v>
+        <v>Nightly</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L154" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Child of Divorce</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>soft pop</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:24</v>
+        <v>3:13</v>
       </c>
       <c r="H155" t="str">
-        <v>Amy Shark</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L155" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Taboo</v>
+        <v>same God</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Taboo - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G156" t="str">
-        <v>3:38</v>
+        <v>3:34</v>
       </c>
       <c r="H156" t="str">
-        <v>Jensen McRae</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L156" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>I'M OK</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>A Rii Set</v>
+        <v>IDCASH</v>
       </c>
       <c r="G157" t="str">
-        <v>2:37</v>
+        <v>2:12</v>
       </c>
       <c r="H157" t="str">
-        <v>Pheelz</v>
+        <v>IDK</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L157" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Butterfly Feelings</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Ritual</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:35</v>
+        <v>3:36</v>
       </c>
       <c r="H158" t="str">
-        <v>Icona Pop</v>
+        <v>070 Shake</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L158" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>F**k the DJ</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>REBECCA</v>
       </c>
       <c r="G159" t="str">
-        <v>2:57</v>
+        <v>2:55</v>
       </c>
       <c r="H159" t="str">
-        <v>Eli</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L159" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Grateful</v>
+        <v>Young Again</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>24</v>
+        <v>EI8HT</v>
       </c>
       <c r="G160" t="str">
-        <v>2:18</v>
+        <v>3:36</v>
       </c>
       <c r="H160" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Shinedown</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L160" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Second Chance</v>
+        <v>skinny dip</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Second Chance - Single</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:06</v>
+        <v>3:12</v>
       </c>
       <c r="H161" t="str">
-        <v>Lukas Graham</v>
+        <v>almost monday</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L161" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G162" t="str">
-        <v>3:49</v>
+        <v>4:14</v>
       </c>
       <c r="H162" t="str">
-        <v>Tommy Lee</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L162" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>DOOM LOOP</v>
+        <v>Better Off</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>Stages</v>
       </c>
       <c r="G163" t="str">
-        <v>4:00</v>
+        <v>3:16</v>
       </c>
       <c r="H163" t="str">
-        <v>PRESIDENT</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L163" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>New York City</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>New York City - Single</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:30</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Anthony Ramos</v>
+        <v>Monaleo</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L164" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I Found You</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>I Found You - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G165" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H165" t="str">
-        <v>TA Thomas</v>
+        <v>R3HAB</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L165" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Just My Type</v>
+        <v>Call Security</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Labor Of Love</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G166" t="str">
-        <v>2:40</v>
+        <v>3:22</v>
       </c>
       <c r="H166" t="str">
-        <v>Blxst</v>
+        <v>Chxrry</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L166" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>teenage drama</v>
+        <v>chaotic</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>teenage drama - Single</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G167" t="str">
-        <v>3:06</v>
+        <v>3:14</v>
       </c>
       <c r="H167" t="str">
-        <v>paris jackson</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L167" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>does it still mean something?</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>only if it matters</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G168" t="str">
-        <v>3:48</v>
+        <v>4:17</v>
       </c>
       <c r="H168" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Love Spells</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L168" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:00</v>
+        <v>3:55</v>
       </c>
       <c r="H169" t="str">
-        <v>Ruel</v>
+        <v>Max McNown</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L169" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G170" t="str">
-        <v>2:25</v>
+        <v>2:10</v>
       </c>
       <c r="H170" t="str">
-        <v>Cruz Beckham</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L170" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Cotton Flower</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G171" t="str">
-        <v>3:53</v>
+        <v>3:24</v>
       </c>
       <c r="H171" t="str">
-        <v>Future Islands</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L171" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>High</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G172" t="str">
-        <v>3:22</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L172" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Comfort</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>So Help Me God</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>5:35</v>
+        <v>2:12</v>
       </c>
       <c r="H173" t="str">
-        <v>Kelsey Lu</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L173" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Skin</v>
+        <v>always knew</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Skin - Single</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:00</v>
+        <v>3:25</v>
       </c>
       <c r="H174" t="str">
-        <v>Alessi Rose</v>
+        <v>Biscits</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L174" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>IDGAF</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>IDGAF - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G175" t="str">
-        <v>2:55</v>
+        <v>2:41</v>
       </c>
       <c r="H175" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L175" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Run Rabbit</v>
+        <v>Let You Down</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G176" t="str">
-        <v>3:09</v>
+        <v>4:14</v>
       </c>
       <c r="H176" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L176" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Starless</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:03</v>
+        <v>4:32</v>
       </c>
       <c r="H177" t="str">
-        <v>CamelPhat</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L177" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>Looking For You</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:01</v>
+        <v>3:19</v>
       </c>
       <c r="H178" t="str">
-        <v>Lane 8</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L178" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>regalametutiempo</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>PROYECTANDO</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:01</v>
+        <v>2:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Julio Caesar</v>
+        <v>Shepherd</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L179" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>On Sight</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Left on RED</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:25</v>
+        <v>3:23</v>
       </c>
       <c r="H180" t="str">
-        <v>REMI</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L180" t="str">
-        <v>On Sight - REMI</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Masks Off</v>
+        <v>dream state</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Masks Off - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H181" t="str">
-        <v>Jesse Welles</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L181" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:49</v>
+        <v>3:39</v>
       </c>
       <c r="H182" t="str">
-        <v>Thee Marloes</v>
+        <v>Mynolia</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L182" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>EXIT 2B</v>
+        <v>Inferno</v>
       </c>
       <c r="G183" t="str">
-        <v>2:11</v>
+        <v>5:25</v>
       </c>
       <c r="H183" t="str">
-        <v>B0YG1RL</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L183" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Money Tree</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Money Tree - Single</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:39</v>
+        <v>2:34</v>
       </c>
       <c r="H184" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L184" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Homerunner</v>
+        <v>FCUK</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Homerunner - Single</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:36</v>
+        <v>2:22</v>
       </c>
       <c r="H185" t="str">
-        <v>slayr</v>
+        <v>H.LLS</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L185" t="str">
-        <v>Homerunner - slayr</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Mail</v>
+        <v>Higher</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Mail - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G186" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H186" t="str">
-        <v>MexikoDro</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L186" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Waste Your Heart</v>
+        <v>B.U.N</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:31</v>
+        <v>3:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L187" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Sleeping Pills</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G188" t="str">
-        <v>3:03</v>
+        <v>3:22</v>
       </c>
       <c r="H188" t="str">
-        <v>Dolder</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L188" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>KODACHROMATIC</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>UNDRA</v>
       </c>
       <c r="G189" t="str">
-        <v>2:53</v>
+        <v>2:49</v>
       </c>
       <c r="H189" t="str">
-        <v>Tiger La Flor</v>
+        <v>reggie</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L189" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>FOMO</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G190" t="str">
-        <v>3:01</v>
+        <v>2:54</v>
       </c>
       <c r="H190" t="str">
-        <v>Anais Cardot</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L190" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Black Fire</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Sulfur Surfer</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G191" t="str">
-        <v>3:37</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Bladee</v>
+        <v>Baby J</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L191" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>6:59</v>
+        <v>3:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L192" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Every Man-Any Man</v>
+        <v>We Fall</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:20</v>
+        <v>4:01</v>
       </c>
       <c r="H193" t="str">
-        <v>Armored Saint</v>
+        <v>MOIO</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L193" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>No Arms</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>From A Distance</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:43</v>
+        <v>3:50</v>
       </c>
       <c r="H194" t="str">
-        <v>156/Silence</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L194" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>It's Neverending</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Neverending</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G195" t="str">
-        <v>8:35</v>
+        <v>4:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Monolord</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L195" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>Iodine</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Neverending</v>
       </c>
       <c r="G196" t="str">
-        <v>3:45</v>
+        <v>3:40</v>
       </c>
       <c r="H196" t="str">
-        <v>Witch Club Satan</v>
+        <v>Monolord</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L196" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>I Speak Forgotten Voices</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>...By the Word...</v>
       </c>
       <c r="G197" t="str">
-        <v>3:20</v>
+        <v>5:01</v>
       </c>
       <c r="H197" t="str">
-        <v>The Darkness</v>
+        <v>Trelldom</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
       </c>
       <c r="L197" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>I Speak Forgotten Voices - Trelldom</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>All Day</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-29</v>
@@ -7899,182 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Feet On Fire</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="G198" t="str">
-        <v>2:29</v>
+        <v>4:45</v>
       </c>
       <c r="H198" t="str">
-        <v>Ben Chapman</v>
+        <v>Flotsam and Jetsam</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
       <c r="L198" t="str">
-        <v>All Day - Ben Chapman</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Sigui</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-05-29</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Massa</v>
-      </c>
-      <c r="G199" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Fatoumata Diawara</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>High Tail</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-05-29</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Where the South Winds Wail</v>
-      </c>
-      <c r="G200" t="str">
-        <v>2:31</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Gitkin</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
-      </c>
-      <c r="L200" t="str">
-        <v>High Tail - Gitkin</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Mice Protection</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-05-29</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Ugly Duckling Union</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:34</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Lowertown</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Mice Protection - Lowertown</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Tóxica</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-05-29</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Caribenya</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:48</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Lido Pimienta</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Tóxica - Lido Pimienta</v>
+        <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>סתיו שמש – היופי שבאמצע⁩</v>
       </c>
       <c r="B2" t="str">
-        <v>1d ago</v>
+        <v>2026-05-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://yosmusic.com/%d7%a1%d7%aa%d7%99%d7%95-%d7%a9%d7%9e%d7%a9-%d7%94%d7%99%d7%95%d7%a4%d7%99-%d7%a9%d7%91%d7%90%d7%9e%d7%a6%d7%a2%e2%81%a9/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1d ago</v>
+        <v>"היופי שבאמצע” של סתיו שמש הוא שיר שמנסה לתאר מצב נפשי מאוד עכשווי: חיים בתוך געגוע מתמשך  לא רק לאדם אחר, אלא לגרסאות קודמות של עצמנו, שיר על זיכרון רגשי, על פצע שלא נעלם אלא מחליף צורה, ועל הניסיון ללמוד</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>סתיו שמש – היופי שבאמצע⁩</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-29</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Julia Cole Music</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-29</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>VictorBiliac</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Jungle4eva</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>DAYTIME TV</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>13d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>13d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B9" t="str">
-        <v>2d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-29</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Bruno Mars</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Keith Urban</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B11" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Nelly Furtado</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B13" t="str">
-        <v>5d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Lainey Wilson</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B15" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Duran Duran</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B16" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Nico Santos</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B17" t="str">
-        <v>5d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B18" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Will Linley</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Kylie Minogue</v>
+        <v>Will Linley</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-29</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>The Offspring</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B22" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>David Gilmour</v>
+        <v>The Offspring</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B23" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Scorpions</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B24" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Scorpions</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B25" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>The Warning</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>paris jackson</v>
+        <v>The Warning</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Minelli</v>
+        <v>paris jackson</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B29" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Maggie Rose</v>
+        <v>Minelli</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-29</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>David Guetta</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-29</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>David Guetta</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-29</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Lauv</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-29</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Icona Pop</v>
+        <v>Lauv</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-29</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Will Swinton</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Dean Lewis</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B37" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Niall Horan</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>RUEL</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>TINI</v>
+        <v>RUEL</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B41" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Charli xcx</v>
+        <v>TINI</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Dua Lipa</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B43" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Matilda Mann</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Ella Langley</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B45" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>kesha</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Holly Humberstone</v>
+        <v>kesha</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Foo Fighters</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>The Analogues</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B50" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Rod Stewart</v>
+        <v>The Analogues</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Blue October</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Far Caspian</v>
+        <v>Blue October</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Kenia Os</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B54" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>12d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-29</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B56" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-29</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B57" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-29</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B58" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-29</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B59" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-29</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B60" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-29</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B61" t="str">
-        <v>13d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-29</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-29</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Evanescence</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-29</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Armin van Buuren</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B64" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-29</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Madison Cunningham</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B65" t="str">
-        <v>13d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-29</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Johnny Orlando</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-29</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Carver Jones</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Jazmin bean</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-29</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Baby Queen</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B69" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-29</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Switchfoot</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-29</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Grace Potter</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B72" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>The All-American Rejects</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-29</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Henry Moodie</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B74" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-29</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Spacey Jane</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-29</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Megan Moroney</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-29</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Matt Hansen</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-29</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-29</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Keith Urban</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-29</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>VALÉ</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-29</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>VALÉ</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-29</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Towa Bird</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-29</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-29</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Little Big Town</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-29</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Becky G</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-29</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Daisy the Great</v>
+        <v>Becky G</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-29</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Towa Bird</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-29</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Madonna</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Ally Salort</v>
+        <v>Madonna</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-29</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Bella White</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-29</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Bella White</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-29</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Towa Bird</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-29</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Miranda Lambert</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-29</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Lady Gaga</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-29</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Gracie Abrams</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-29</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-29</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Martin Garrix</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-29</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Jorja Smith</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-29</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>LP</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-29</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>The Rolling Stones</v>
+        <v>LP</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-29</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Oasis</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-29</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Oasis</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>hate that i made you love me</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>petal</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Ariana Grande</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Come Inside</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>petal</v>
       </c>
       <c r="G103" t="str">
-        <v>3:13</v>
+        <v>3:17</v>
       </c>
       <c r="H103" t="str">
-        <v>Paul McCartney</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L103" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Game Time</v>
+        <v>Come Inside</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H104" t="str">
-        <v>Future</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>Game Time - Future</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Game Time</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:36</v>
+        <v>3:26</v>
       </c>
       <c r="H105" t="str">
-        <v>Bossman Dlow</v>
+        <v>Future</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L105" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Aquel diciembre</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:22</v>
+        <v>2:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Young Miko</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L106" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Handle</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Blue Island</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G107" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H107" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Young Miko</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L107" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>The Wave</v>
+        <v>Handle</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sunshine</v>
+        <v>Blue Island</v>
       </c>
       <c r="G108" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H108" t="str">
-        <v>Jungle</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L108" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>STOP</v>
+        <v>The Wave</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G109" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H109" t="str">
-        <v>Bella Kay</v>
+        <v>Jungle</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L109" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>STOP</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Apple Music Sessions</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H110" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L110" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Talk On The Hill</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>The Thread</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G111" t="str">
-        <v>3:27</v>
+        <v>3:08</v>
       </c>
       <c r="H111" t="str">
-        <v>WILLOW</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L111" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No Fear</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Thread</v>
       </c>
       <c r="G112" t="str">
-        <v>3:38</v>
+        <v>3:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Iceage</v>
+        <v>WILLOW</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L112" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>No Fear</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Big Mama</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G113" t="str">
-        <v>3:11</v>
+        <v>3:38</v>
       </c>
       <c r="H113" t="str">
-        <v>Latto</v>
+        <v>Iceage</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L113" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sad Girls</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G114" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H114" t="str">
-        <v>Bebe Rexha</v>
+        <v>Latto</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L114" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:35</v>
+        <v>2:48</v>
       </c>
       <c r="H115" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Rubio</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>La Voz Favorita</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:42</v>
+        <v>3:35</v>
       </c>
       <c r="H116" t="str">
-        <v>Jay Wheeler</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L116" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Pary</v>
+        <v>Rubio</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Con dolor - EP</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G117" t="str">
-        <v>2:52</v>
+        <v>4:42</v>
       </c>
       <c r="H117" t="str">
-        <v>Grupo Frontera</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L117" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Think As You Drunk</v>
+        <v>Pary</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>That's Just Me</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G118" t="str">
-        <v>3:48</v>
+        <v>2:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Riley Green</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L118" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Play Your Games</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Play Your Games - Single</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G119" t="str">
-        <v>3:15</v>
+        <v>3:48</v>
       </c>
       <c r="H119" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Riley Green</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L119" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:47</v>
+        <v>3:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Tom Morello</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:49</v>
+        <v>2:47</v>
       </c>
       <c r="H121" t="str">
-        <v>Blood Orange</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L121" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>minute</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ghosted - EP</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:59</v>
+        <v>4:49</v>
       </c>
       <c r="H122" t="str">
-        <v>Saint Harison</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L122" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>THE LIVING</v>
+        <v>minute</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H123" t="str">
-        <v>Labrinth</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L123" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thug</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thug - Single</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>2:48</v>
       </c>
       <c r="H124" t="str">
-        <v>G Herbo</v>
+        <v>Labrinth</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L124" t="str">
-        <v>Thug - G Herbo</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Clap</v>
+        <v>Thug</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Clap - Single</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:04</v>
+        <v>2:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Polo G</v>
+        <v>G Herbo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L125" t="str">
-        <v>Clap - Polo G</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Clap</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:47</v>
+        <v>2:04</v>
       </c>
       <c r="H126" t="str">
-        <v>YG</v>
+        <v>Polo G</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L126" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G127" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H127" t="str">
-        <v>Jessie Reyez</v>
+        <v>YG</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Joshua Tree</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G128" t="str">
         <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Hans Zimmer</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L128" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Mi Gran Amor</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:37</v>
+        <v>2:50</v>
       </c>
       <c r="H129" t="str">
-        <v>Santana</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L129" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>london</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>stardust - EP</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>3:37</v>
       </c>
       <c r="H130" t="str">
-        <v>Freya Skye</v>
+        <v>Santana</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L130" t="str">
-        <v>london - Freya Skye</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Caution</v>
+        <v>london</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>2:43</v>
+        <v>3:23</v>
       </c>
       <c r="H131" t="str">
-        <v>NMIXX</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L131" t="str">
-        <v>Caution - NMIXX</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Caution</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G132" t="str">
-        <v>3:07</v>
+        <v>2:43</v>
       </c>
       <c r="H132" t="str">
-        <v>aespa</v>
+        <v>NMIXX</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L132" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G133" t="str">
-        <v>2:58</v>
+        <v>3:07</v>
       </c>
       <c r="H133" t="str">
-        <v>Cody Johnson</v>
+        <v>aespa</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L133" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Cheap Thrills</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G134" t="str">
-        <v>2:42</v>
+        <v>2:58</v>
       </c>
       <c r="H134" t="str">
-        <v>Gavin Adcock</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L134" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ME VALE V</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>ACOMODO</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H135" t="str">
-        <v>Tito Double P</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L135" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bug In The Cake</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Be Sweet To Me</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G136" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H136" t="str">
-        <v>Violet Grohl</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L136" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Coil</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Rumspringa</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G137" t="str">
-        <v>3:54</v>
+        <v>2:48</v>
       </c>
       <c r="H137" t="str">
-        <v>ear</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L137" t="str">
-        <v>Coil - ear</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Coil</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G138" t="str">
-        <v>3:30</v>
+        <v>3:54</v>
       </c>
       <c r="H138" t="str">
-        <v>Kneecap</v>
+        <v>ear</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Out of my Head</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:04</v>
+        <v>3:30</v>
       </c>
       <c r="H139" t="str">
-        <v>Cara Delevingne</v>
+        <v>Kneecap</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L139" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Passenger Princess</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:18</v>
+        <v>3:04</v>
       </c>
       <c r="H140" t="str">
-        <v>Perrie</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L140" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Man of the House</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>SE9</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:35</v>
+        <v>3:18</v>
       </c>
       <c r="H141" t="str">
-        <v>Skye Newman</v>
+        <v>Perrie</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L141" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Man of the House</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G142" t="str">
-        <v>2:37</v>
+        <v>2:35</v>
       </c>
       <c r="H142" t="str">
-        <v>MEEK</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L142" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:34</v>
+        <v>2:37</v>
       </c>
       <c r="H143" t="str">
-        <v>ILLENIUM</v>
+        <v>MEEK</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>4:34</v>
       </c>
       <c r="H144" t="str">
-        <v>Lily Allen</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L144" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ABOVE IT</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:45</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Andy Mineo</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L145" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:15</v>
+        <v>1:45</v>
       </c>
       <c r="H146" t="str">
-        <v>Forrest Frank</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L146" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Is It Over Now?</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:39</v>
+        <v>4:15</v>
       </c>
       <c r="H147" t="str">
-        <v>Elderbrook</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L147" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>12 Steps</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>12 Steps - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:11</v>
+        <v>3:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L148" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Over And Over</v>
+        <v>12 Steps</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>It's A Dying Art</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:38</v>
+        <v>3:11</v>
       </c>
       <c r="H149" t="str">
-        <v>Little Big Town</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L149" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>AMAPOLA</v>
+        <v>Over And Over</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ricky y Mau</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G150" t="str">
-        <v>2:22</v>
+        <v>4:38</v>
       </c>
       <c r="H150" t="str">
-        <v>Mau y Ricky</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L150" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Mad About It</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mad About It - Single</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G151" t="str">
-        <v>2:37</v>
+        <v>2:22</v>
       </c>
       <c r="H151" t="str">
-        <v>Dasha</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L151" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Love’s a Gun</v>
+        <v>Mad About It</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:59</v>
+        <v>2:37</v>
       </c>
       <c r="H152" t="str">
-        <v>Daniel Seavey</v>
+        <v>Dasha</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L152" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Long Story Short</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Long Story Short - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H153" t="str">
-        <v>Knox</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L153" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>blue jeans</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>blue jeans - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>2:48</v>
       </c>
       <c r="H154" t="str">
-        <v>Nightly</v>
+        <v>Knox</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L154" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Que Gacho</v>
+        <v>blue jeans</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Que Gacho - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:13</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nightly</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L155" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>same God</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:34</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>Alana Springsteen</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L156" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>emotional swaggage</v>
+        <v>same God</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>IDCASH</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G157" t="str">
-        <v>2:12</v>
+        <v>3:34</v>
       </c>
       <c r="H157" t="str">
-        <v>IDK</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L157" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Baby Driver</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Baby Driver - Single</v>
+        <v>IDCASH</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>2:12</v>
       </c>
       <c r="H158" t="str">
-        <v>070 Shake</v>
+        <v>IDK</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L158" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>More! More! More!</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>REBECCA</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:55</v>
+        <v>3:36</v>
       </c>
       <c r="H159" t="str">
-        <v>Becky Hill</v>
+        <v>070 Shake</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L159" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Young Again</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>EI8HT</v>
+        <v>REBECCA</v>
       </c>
       <c r="G160" t="str">
-        <v>3:36</v>
+        <v>2:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Shinedown</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L160" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>skinny dip</v>
+        <v>Young Again</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>skinny dip - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G161" t="str">
-        <v>3:12</v>
+        <v>3:36</v>
       </c>
       <c r="H161" t="str">
-        <v>almost monday</v>
+        <v>Shinedown</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L161" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>skinny dip</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>girls like girls the album</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:14</v>
+        <v>3:12</v>
       </c>
       <c r="H162" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>almost monday</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L162" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Better Off</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Stages</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G163" t="str">
-        <v>3:16</v>
+        <v>4:14</v>
       </c>
       <c r="H163" t="str">
-        <v>Lauren Alaina</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L163" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Better Off</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Stages</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:16</v>
       </c>
       <c r="H164" t="str">
-        <v>Monaleo</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Lost in translation...</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:30</v>
+        <v>2:48</v>
       </c>
       <c r="H165" t="str">
-        <v>R3HAB</v>
+        <v>Monaleo</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L165" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Call Security</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G166" t="str">
-        <v>3:22</v>
+        <v>3:30</v>
       </c>
       <c r="H166" t="str">
-        <v>Chxrry</v>
+        <v>R3HAB</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L166" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>chaotic</v>
+        <v>Call Security</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>scars to prove it</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G167" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H167" t="str">
-        <v>Hailey Picardi</v>
+        <v>Chxrry</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L167" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Keep It To Yourself</v>
+        <v>chaotic</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G168" t="str">
-        <v>4:17</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>Love Spells</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L168" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Something to Someone</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Something to Someone - Single</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G169" t="str">
-        <v>3:55</v>
+        <v>4:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Max McNown</v>
+        <v>Love Spells</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L169" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Hours: High Noon</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:10</v>
+        <v>3:55</v>
       </c>
       <c r="H170" t="str">
-        <v>Cautious Clay</v>
+        <v>Max McNown</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L170" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Scoreboard</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G171" t="str">
-        <v>3:24</v>
+        <v>2:10</v>
       </c>
       <c r="H171" t="str">
-        <v>Gabriella Rose</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L171" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>High</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:24</v>
       </c>
       <c r="H172" t="str">
-        <v>Nia Smith</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L172" t="str">
-        <v>High - Nia Smith</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Ay Gyal</v>
+        <v>High</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G173" t="str">
-        <v>2:12</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>1Ski OG</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L173" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>always knew</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>always knew - Single</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:25</v>
+        <v>2:12</v>
       </c>
       <c r="H174" t="str">
-        <v>Biscits</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L174" t="str">
-        <v>always knew - Biscits</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cigarette Burns</v>
+        <v>always knew</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:41</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>Corey Kent</v>
+        <v>Biscits</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L175" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Let You Down</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>El Relevo</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G176" t="str">
-        <v>4:14</v>
+        <v>2:41</v>
       </c>
       <c r="H176" t="str">
-        <v>Luis Figueroa</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L176" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Starless</v>
+        <v>Let You Down</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Starless - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G177" t="str">
-        <v>4:32</v>
+        <v>4:14</v>
       </c>
       <c r="H177" t="str">
-        <v>A Perfect Circle</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L177" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking For You</v>
+        <v>Starless</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking For You - Single</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:19</v>
+        <v>4:32</v>
       </c>
       <c r="H178" t="str">
-        <v>Gable Price and Friends</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>FOCUSED</v>
+        <v>Looking For You</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:23</v>
+        <v>3:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Shepherd</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L179" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:23</v>
+        <v>2:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Shepherd</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L180" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>dream state</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>dream state - Single</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L181" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>dream state</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:39</v>
+        <v>4:01</v>
       </c>
       <c r="H182" t="str">
-        <v>Mynolia</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L182" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Inferno</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>5:25</v>
+        <v>3:39</v>
       </c>
       <c r="H183" t="str">
-        <v>Boards of Canada</v>
+        <v>Mynolia</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L183" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G184" t="str">
-        <v>2:34</v>
+        <v>5:25</v>
       </c>
       <c r="H184" t="str">
-        <v>Delroy Edwards</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L184" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>FCUK</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>FCUK - Single</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:22</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>H.LLS</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L185" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Higher</v>
+        <v>FCUK</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:06</v>
+        <v>2:22</v>
       </c>
       <c r="H186" t="str">
-        <v>Francis of Delirium</v>
+        <v>H.LLS</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L186" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>B.U.N</v>
+        <v>Higher</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>B.U.N - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G187" t="str">
-        <v>3:43</v>
+        <v>4:06</v>
       </c>
       <c r="H187" t="str">
-        <v>Roll Deep</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L187" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>B.U.N</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Here Because of Hope</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H188" t="str">
-        <v>Ezra Collective</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L188" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>UNDRA</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G189" t="str">
-        <v>2:49</v>
+        <v>3:22</v>
       </c>
       <c r="H189" t="str">
-        <v>reggie</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L189" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>UNDRA</v>
       </c>
       <c r="G190" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H190" t="str">
-        <v>Johnny Huynh</v>
+        <v>reggie</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L190" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Fallen Angel</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>You Don't Know My Name</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G191" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby J</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L191" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Last Encounter</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G192" t="str">
-        <v>3:04</v>
+        <v>3:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Sofia Camara</v>
+        <v>Baby J</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L192" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>We Fall</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>We Fall - Single</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:01</v>
+        <v>3:04</v>
       </c>
       <c r="H193" t="str">
-        <v>MOIO</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L193" t="str">
-        <v>We Fall - MOIO</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Don't Know Me</v>
+        <v>We Fall</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:50</v>
+        <v>4:01</v>
       </c>
       <c r="H194" t="str">
-        <v>Isabel Dumaa</v>
+        <v>MOIO</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L194" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>House Of Mirrors</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:04</v>
+        <v>3:50</v>
       </c>
       <c r="H195" t="str">
-        <v>All Them Witches</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L195" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Iodine</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Neverending</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G196" t="str">
-        <v>3:40</v>
+        <v>4:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Monolord</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L196" t="str">
-        <v>Iodine - Monolord</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Iodine</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-29</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>...By the Word...</v>
+        <v>Neverending</v>
       </c>
       <c r="G197" t="str">
-        <v>5:01</v>
+        <v>3:40</v>
       </c>
       <c r="H197" t="str">
-        <v>Trelldom</v>
+        <v>Monolord</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L197" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>I Speak Forgotten Voices</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>...By the Word...</v>
+      </c>
+      <c r="G198" t="str">
+        <v>5:01</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Trelldom</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+      </c>
+      <c r="L198" t="str">
+        <v>I Speak Forgotten Voices - Trelldom</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-05-29</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:45</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Flotsam and Jetsam</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סתיו שמש – היופי שבאמצע⁩</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-29</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%aa%d7%99%d7%95-%d7%a9%d7%9e%d7%a9-%d7%94%d7%99%d7%95%d7%a4%d7%99-%d7%a9%d7%91%d7%90%d7%9e%d7%a6%d7%a2%e2%81%a9/</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"היופי שבאמצע” של סתיו שמש הוא שיר שמנסה לתאר מצב נפשי מאוד עכשווי: חיים בתוך געגוע מתמשך  לא רק לאדם אחר, אלא לגרסאות קודמות של עצמנו, שיר על זיכרון רגשי, על פצע שלא נעלם אלא מחליף צורה, ועל הניסיון ללמוד</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Dua Lipa</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סתיו שמש – היופי שבאמצע⁩</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-29</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Dagny</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-29</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Julia Cole Music</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>VictorBiliac</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Dogpark</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Jungle4eva</v>
+        <v>elijah woods</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>DAYTIME TV</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>13 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-29</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>13 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Bruno Mars</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Keith Urban</v>
+        <v>Dasha</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Nelly Furtado</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Max McNown</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Lainey Wilson</v>
+        <v>Knox</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Duran Duran</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Nico Santos</v>
+        <v>Alexander James</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>DEF LEPPARD</v>
+        <v>almost monday</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Will Linley</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Kylie Minogue</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-29</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Billy Raffoul</v>
+        <v>Santana</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>The Offspring</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>David Gilmour</v>
+        <v>Charley</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Scorpions</v>
+        <v>David Guetta</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>The Warning</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>paris jackson</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Minelli</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-29</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Maggie Rose</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-29</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>David Guetta</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-29</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-29</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Lauv</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-29</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Icona Pop</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Will Swinton</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Dean Lewis</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Niall Horan</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>RUEL</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>TINI</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Charli xcx</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Dua Lipa</v>
+        <v>Will Linley</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Matilda Mann</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Ella Langley</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Nothing But Thieves</v>
+        <v>The Offspring</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>kesha</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Holly Humberstone</v>
+        <v>Scorpions</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Foo Fighters</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The Analogues</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Rod Stewart</v>
+        <v>The Warning</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Blue October</v>
+        <v>paris jackson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Far Caspian</v>
+        <v>Minelli</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Kenia Os</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-29</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Purple Disco Machine</v>
+        <v>David Guetta</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-29</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-29</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Lauv</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-29</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-29</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-29</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-29</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-29</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Evanescence</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-29</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-29</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Armin van Buuren</v>
+        <v>RUEL</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-29</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Madison Cunningham</v>
+        <v>TINI</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-29</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Johnny Orlando</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Carver Jones</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-29</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Jazmin bean</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-29</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Baby Queen</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-29</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Switchfoot</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Grace Potter</v>
+        <v>kesha</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-29</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>The All-American Rejects</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-29</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Henry Moodie</v>
+        <v>The Analogues</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-29</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Spacey Jane</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-29</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Megan Moroney</v>
+        <v>Blue October</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-29</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Matt Hansen</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-29</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Matt Hansen</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-29</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Keith Urban</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-29</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>VALÉ</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-29</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-29</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Towa Bird</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-29</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-29</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Little Big Town</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-29</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Becky G</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-29</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Daisy the Great</v>
+        <v>Evanescence</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-29</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Towa Bird</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Madonna</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-29</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Ally Salort</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-29</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Bella White</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-29</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-29</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Towa Bird</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-29</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Miranda Lambert</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-29</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Lady Gaga</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-29</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Gracie Abrams</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-29</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-29</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Martin Garrix</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-29</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Jorja Smith</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-29</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>LP</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-29</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The Rolling Stones</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-29</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Oasis</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>petal</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H102" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L102" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>hate that i made you love me</v>
+        <v>Come Inside</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>petal</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v>3:13</v>
       </c>
       <c r="H103" t="str">
-        <v>Ariana Grande</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L103" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Come Inside</v>
+        <v>Game Time</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>Future</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L104" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Game Time</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:26</v>
+        <v>2:36</v>
       </c>
       <c r="H105" t="str">
-        <v>Future</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L105" t="str">
-        <v>Game Time - Future</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G106" t="str">
-        <v>2:36</v>
+        <v>3:22</v>
       </c>
       <c r="H106" t="str">
-        <v>Bossman Dlow</v>
+        <v>Young Miko</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L106" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Aquel diciembre</v>
+        <v>Handle</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Blue Island</v>
       </c>
       <c r="G107" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H107" t="str">
-        <v>Young Miko</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L107" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Handle</v>
+        <v>The Wave</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Blue Island</v>
+        <v>Sunshine</v>
       </c>
       <c r="G108" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H108" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Jungle</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L108" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>The Wave</v>
+        <v>STOP</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sunshine</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:22</v>
+        <v>2:56</v>
       </c>
       <c r="H109" t="str">
-        <v>Jungle</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L109" t="str">
-        <v>The Wave - Jungle</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>STOP</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G110" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H110" t="str">
-        <v>Bella Kay</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L110" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Apple Music Sessions</v>
+        <v>The Thread</v>
       </c>
       <c r="G111" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H111" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>WILLOW</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L111" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Talk On The Hill</v>
+        <v>No Fear</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>The Thread</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G112" t="str">
-        <v>3:27</v>
+        <v>3:38</v>
       </c>
       <c r="H112" t="str">
-        <v>WILLOW</v>
+        <v>Iceage</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L112" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No Fear</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Big Mama</v>
       </c>
       <c r="G113" t="str">
-        <v>3:38</v>
+        <v>3:11</v>
       </c>
       <c r="H113" t="str">
-        <v>Iceage</v>
+        <v>Latto</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L113" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Big Mama</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H114" t="str">
-        <v>Latto</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L114" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Sad Girls</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H115" t="str">
-        <v>Bebe Rexha</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L115" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Rubio</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G116" t="str">
-        <v>3:35</v>
+        <v>4:42</v>
       </c>
       <c r="H116" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Rubio</v>
+        <v>Pary</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>La Voz Favorita</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>4:42</v>
+        <v>2:52</v>
       </c>
       <c r="H117" t="str">
-        <v>Jay Wheeler</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L117" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Pary</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Con dolor - EP</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G118" t="str">
-        <v>2:52</v>
+        <v>3:48</v>
       </c>
       <c r="H118" t="str">
-        <v>Grupo Frontera</v>
+        <v>Riley Green</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L118" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Think As You Drunk</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>That's Just Me</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:48</v>
+        <v>3:15</v>
       </c>
       <c r="H119" t="str">
-        <v>Riley Green</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L119" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Play Your Games</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Play Your Games - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:15</v>
+        <v>2:47</v>
       </c>
       <c r="H120" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L120" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:47</v>
+        <v>4:49</v>
       </c>
       <c r="H121" t="str">
-        <v>Tom Morello</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>minute</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>4:49</v>
+        <v>2:59</v>
       </c>
       <c r="H122" t="str">
-        <v>Blood Orange</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L122" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>minute</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ghosted - EP</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>2:59</v>
+        <v>2:48</v>
       </c>
       <c r="H123" t="str">
-        <v>Saint Harison</v>
+        <v>Labrinth</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L123" t="str">
-        <v>minute - Saint Harison</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>THE LIVING</v>
+        <v>Thug</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:48</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Labrinth</v>
+        <v>G Herbo</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L124" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thug</v>
+        <v>Clap</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Thug - Single</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:25</v>
+        <v>2:04</v>
       </c>
       <c r="H125" t="str">
-        <v>G Herbo</v>
+        <v>Polo G</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L125" t="str">
-        <v>Thug - G Herbo</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Clap</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Clap - Single</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G126" t="str">
-        <v>2:04</v>
+        <v>2:47</v>
       </c>
       <c r="H126" t="str">
-        <v>Polo G</v>
+        <v>YG</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L126" t="str">
-        <v>Clap - Polo G</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>GANG BIZNESS</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G127" t="str">
-        <v>2:47</v>
+        <v>2:50</v>
       </c>
       <c r="H127" t="str">
-        <v>YG</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L127" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G128" t="str">
         <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Jessie Reyez</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L128" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Joshua Tree</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:50</v>
+        <v>3:37</v>
       </c>
       <c r="H129" t="str">
-        <v>Hans Zimmer</v>
+        <v>Santana</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L129" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Mi Gran Amor</v>
+        <v>london</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:37</v>
+        <v>3:23</v>
       </c>
       <c r="H130" t="str">
-        <v>Santana</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L130" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>london</v>
+        <v>Caution</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>stardust - EP</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G131" t="str">
-        <v>3:23</v>
+        <v>2:43</v>
       </c>
       <c r="H131" t="str">
-        <v>Freya Skye</v>
+        <v>NMIXX</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L131" t="str">
-        <v>london - Freya Skye</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Caution</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G132" t="str">
-        <v>2:43</v>
+        <v>3:07</v>
       </c>
       <c r="H132" t="str">
-        <v>NMIXX</v>
+        <v>aespa</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L132" t="str">
-        <v>Caution - NMIXX</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G133" t="str">
-        <v>3:07</v>
+        <v>2:58</v>
       </c>
       <c r="H133" t="str">
-        <v>aespa</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L133" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:58</v>
+        <v>2:42</v>
       </c>
       <c r="H134" t="str">
-        <v>Cody Johnson</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L134" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Cheap Thrills</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G135" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H135" t="str">
-        <v>Gavin Adcock</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L135" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ME VALE V</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>ACOMODO</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G136" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H136" t="str">
-        <v>Tito Double P</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L136" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Bug In The Cake</v>
+        <v>Coil</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G137" t="str">
-        <v>2:48</v>
+        <v>3:54</v>
       </c>
       <c r="H137" t="str">
-        <v>Violet Grohl</v>
+        <v>ear</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L137" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Coil</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Rumspringa</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:54</v>
+        <v>3:30</v>
       </c>
       <c r="H138" t="str">
-        <v>ear</v>
+        <v>Kneecap</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L138" t="str">
-        <v>Coil - ear</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:30</v>
+        <v>3:04</v>
       </c>
       <c r="H139" t="str">
-        <v>Kneecap</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Out of my Head</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:04</v>
+        <v>3:18</v>
       </c>
       <c r="H140" t="str">
-        <v>Cara Delevingne</v>
+        <v>Perrie</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L140" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Passenger Princess</v>
+        <v>Man of the House</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G141" t="str">
-        <v>3:18</v>
+        <v>2:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Perrie</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L141" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Man of the House</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>SE9</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:35</v>
+        <v>2:37</v>
       </c>
       <c r="H142" t="str">
-        <v>Skye Newman</v>
+        <v>MEEK</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L142" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:37</v>
+        <v>4:34</v>
       </c>
       <c r="H143" t="str">
-        <v>MEEK</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L143" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>4:34</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>ILLENIUM</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L144" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>1:45</v>
       </c>
       <c r="H145" t="str">
-        <v>Lily Allen</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L145" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ABOVE IT</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:45</v>
+        <v>4:15</v>
       </c>
       <c r="H146" t="str">
-        <v>Andy Mineo</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L146" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:15</v>
+        <v>3:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Forrest Frank</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L147" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Is It Over Now?</v>
+        <v>12 Steps</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:39</v>
+        <v>3:11</v>
       </c>
       <c r="H148" t="str">
-        <v>Elderbrook</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L148" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>12 Steps</v>
+        <v>Over And Over</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>12 Steps - Single</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G149" t="str">
-        <v>3:11</v>
+        <v>4:38</v>
       </c>
       <c r="H149" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L149" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Over And Over</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>It's A Dying Art</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G150" t="str">
-        <v>4:38</v>
+        <v>2:22</v>
       </c>
       <c r="H150" t="str">
-        <v>Little Big Town</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L150" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>AMAPOLA</v>
+        <v>Mad About It</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ricky y Mau</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:22</v>
+        <v>2:37</v>
       </c>
       <c r="H151" t="str">
-        <v>Mau y Ricky</v>
+        <v>Dasha</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L151" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mad About It</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mad About It - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:37</v>
+        <v>2:59</v>
       </c>
       <c r="H152" t="str">
-        <v>Dasha</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L152" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Love’s a Gun</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:59</v>
+        <v>2:48</v>
       </c>
       <c r="H153" t="str">
-        <v>Daniel Seavey</v>
+        <v>Knox</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L153" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Long Story Short</v>
+        <v>blue jeans</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Long Story Short - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:48</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Knox</v>
+        <v>Nightly</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L154" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>blue jeans</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>blue jeans - Single</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>3:13</v>
       </c>
       <c r="H155" t="str">
-        <v>Nightly</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L155" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Que Gacho</v>
+        <v>same God</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Que Gacho - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G156" t="str">
-        <v>3:13</v>
+        <v>3:34</v>
       </c>
       <c r="H156" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L156" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>same God</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>IDCASH</v>
       </c>
       <c r="G157" t="str">
-        <v>3:34</v>
+        <v>2:12</v>
       </c>
       <c r="H157" t="str">
-        <v>Alana Springsteen</v>
+        <v>IDK</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L157" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>emotional swaggage</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>IDCASH</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:12</v>
+        <v>3:36</v>
       </c>
       <c r="H158" t="str">
-        <v>IDK</v>
+        <v>070 Shake</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L158" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Baby Driver</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Baby Driver - Single</v>
+        <v>REBECCA</v>
       </c>
       <c r="G159" t="str">
-        <v>3:36</v>
+        <v>2:55</v>
       </c>
       <c r="H159" t="str">
-        <v>070 Shake</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L159" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>More! More! More!</v>
+        <v>Young Again</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>REBECCA</v>
+        <v>EI8HT</v>
       </c>
       <c r="G160" t="str">
-        <v>2:55</v>
+        <v>3:36</v>
       </c>
       <c r="H160" t="str">
-        <v>Becky Hill</v>
+        <v>Shinedown</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L160" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Young Again</v>
+        <v>skinny dip</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>EI8HT</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:36</v>
+        <v>3:12</v>
       </c>
       <c r="H161" t="str">
-        <v>Shinedown</v>
+        <v>almost monday</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L161" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>skinny dip</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>skinny dip - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G162" t="str">
-        <v>3:12</v>
+        <v>4:14</v>
       </c>
       <c r="H162" t="str">
-        <v>almost monday</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L162" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>Better Off</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>girls like girls the album</v>
+        <v>Stages</v>
       </c>
       <c r="G163" t="str">
-        <v>4:14</v>
+        <v>3:16</v>
       </c>
       <c r="H163" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L163" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Better Off</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Stages</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:16</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Lauren Alaina</v>
+        <v>Monaleo</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L164" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G165" t="str">
-        <v>2:48</v>
+        <v>3:30</v>
       </c>
       <c r="H165" t="str">
-        <v>Monaleo</v>
+        <v>R3HAB</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Lost in translation...</v>
+        <v>Call Security</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Dream inside a dream…</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G166" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H166" t="str">
-        <v>R3HAB</v>
+        <v>Chxrry</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L166" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Call Security</v>
+        <v>chaotic</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G167" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H167" t="str">
-        <v>Chxrry</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L167" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>chaotic</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>scars to prove it</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>4:17</v>
       </c>
       <c r="H168" t="str">
-        <v>Hailey Picardi</v>
+        <v>Love Spells</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L168" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Keep It To Yourself</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:17</v>
+        <v>3:55</v>
       </c>
       <c r="H169" t="str">
-        <v>Love Spells</v>
+        <v>Max McNown</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L169" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Something to Someone</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Something to Someone - Single</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G170" t="str">
-        <v>3:55</v>
+        <v>2:10</v>
       </c>
       <c r="H170" t="str">
-        <v>Max McNown</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L170" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Hours: High Noon</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G171" t="str">
-        <v>2:10</v>
+        <v>3:24</v>
       </c>
       <c r="H171" t="str">
-        <v>Cautious Clay</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L171" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Scoreboard</v>
+        <v>High</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G172" t="str">
-        <v>3:24</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>Gabriella Rose</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L172" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>High</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>2:12</v>
       </c>
       <c r="H173" t="str">
-        <v>Nia Smith</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L173" t="str">
-        <v>High - Nia Smith</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ay Gyal</v>
+        <v>always knew</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:12</v>
+        <v>3:25</v>
       </c>
       <c r="H174" t="str">
-        <v>1Ski OG</v>
+        <v>Biscits</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L174" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>always knew</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>always knew - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G175" t="str">
-        <v>3:25</v>
+        <v>2:41</v>
       </c>
       <c r="H175" t="str">
-        <v>Biscits</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L175" t="str">
-        <v>always knew - Biscits</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Cigarette Burns</v>
+        <v>Let You Down</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>El Relevo</v>
       </c>
       <c r="G176" t="str">
-        <v>2:41</v>
+        <v>4:14</v>
       </c>
       <c r="H176" t="str">
-        <v>Corey Kent</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L176" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Let You Down</v>
+        <v>Starless</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>El Relevo</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:14</v>
+        <v>4:32</v>
       </c>
       <c r="H177" t="str">
-        <v>Luis Figueroa</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L177" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Starless</v>
+        <v>Looking For You</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Starless - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:32</v>
+        <v>3:19</v>
       </c>
       <c r="H178" t="str">
-        <v>A Perfect Circle</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L178" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Looking For You</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Looking For You - Single</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:19</v>
+        <v>2:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Shepherd</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L179" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>FOCUSED</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:23</v>
+        <v>3:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Shepherd</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L180" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>dream state</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H181" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L181" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>dream state</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>dream state - Single</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:01</v>
+        <v>3:39</v>
       </c>
       <c r="H182" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Mynolia</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L182" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G183" t="str">
-        <v>3:39</v>
+        <v>5:25</v>
       </c>
       <c r="H183" t="str">
-        <v>Mynolia</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L183" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Inferno</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>5:25</v>
+        <v>2:34</v>
       </c>
       <c r="H184" t="str">
-        <v>Boards of Canada</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L184" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>FCUK</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:34</v>
+        <v>2:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Delroy Edwards</v>
+        <v>H.LLS</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L185" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>FCUK</v>
+        <v>Higher</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>FCUK - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G186" t="str">
-        <v>2:22</v>
+        <v>4:06</v>
       </c>
       <c r="H186" t="str">
-        <v>H.LLS</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L186" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Higher</v>
+        <v>B.U.N</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:06</v>
+        <v>3:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Francis of Delirium</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L187" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>B.U.N</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>B.U.N - Single</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G188" t="str">
-        <v>3:43</v>
+        <v>3:22</v>
       </c>
       <c r="H188" t="str">
-        <v>Roll Deep</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L188" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Here Because of Hope</v>
+        <v>UNDRA</v>
       </c>
       <c r="G189" t="str">
-        <v>3:22</v>
+        <v>2:49</v>
       </c>
       <c r="H189" t="str">
-        <v>Ezra Collective</v>
+        <v>reggie</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L189" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>UNDRA</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G190" t="str">
-        <v>2:49</v>
+        <v>2:54</v>
       </c>
       <c r="H190" t="str">
-        <v>reggie</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L190" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G191" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Johnny Huynh</v>
+        <v>Baby J</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L191" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Fallen Angel</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>You Don't Know My Name</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Baby J</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L192" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Last Encounter</v>
+        <v>We Fall</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:04</v>
+        <v>4:01</v>
       </c>
       <c r="H193" t="str">
-        <v>Sofia Camara</v>
+        <v>MOIO</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L193" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>We Fall</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>We Fall - Single</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:01</v>
+        <v>3:50</v>
       </c>
       <c r="H194" t="str">
-        <v>MOIO</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L194" t="str">
-        <v>We Fall - MOIO</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>You Don't Know Me</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G195" t="str">
-        <v>3:50</v>
+        <v>4:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Isabel Dumaa</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L195" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>Iodine</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>House Of Mirrors</v>
+        <v>Neverending</v>
       </c>
       <c r="G196" t="str">
-        <v>4:04</v>
+        <v>3:40</v>
       </c>
       <c r="H196" t="str">
-        <v>All Them Witches</v>
+        <v>Monolord</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L196" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Iodine</v>
+        <v>I Speak Forgotten Voices</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Neverending</v>
+        <v>...By the Word...</v>
       </c>
       <c r="G197" t="str">
-        <v>3:40</v>
+        <v>5:01</v>
       </c>
       <c r="H197" t="str">
-        <v>Monolord</v>
+        <v>Trelldom</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
       </c>
       <c r="L197" t="str">
-        <v>Iodine - Monolord</v>
+        <v>I Speak Forgotten Voices - Trelldom</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-29</v>
@@ -7899,68 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>...By the Word...</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="G198" t="str">
-        <v>5:01</v>
+        <v>4:45</v>
       </c>
       <c r="H198" t="str">
-        <v>Trelldom</v>
+        <v>Flotsam and Jetsam</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
       <c r="L198" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-05-29</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="G199" t="str">
-        <v>4:45</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Flotsam and Jetsam</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
-      </c>
-      <c r="L199" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>אור קודאי – פירורים</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>2026-05-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a7%d7%95%d7%93%d7%90%d7%99-%d7%a4%d7%99%d7%a8%d7%95%d7%a8%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>אור קודאי שר בלדה מלנכולית שנשענת פחות על עלילה ויותר על תחושה – תחושת ריקנות אחרי אהבה שנשחקה עד שלא נותר ממנה כמעט דבר. הדימוי "פירורים" מבטא לא שברון לב דרמטי, אלא שאריות. של משהו שהיה פעם שלם, חם ומזין,</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Dua Lipa</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>אור קודאי – פירורים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-29</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dagny</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-29</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Dagny</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B5" t="str">
-        <v>5 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Dogpark</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>elijah woods</v>
+        <v>Dogpark</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B8" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Lauren Alaina</v>
+        <v>elijah woods</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-29</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>NIGHTLY</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Dasha</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ariana Grande</v>
+        <v>Dasha</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B13" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Max McNown</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v>Max McNown</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Knox</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Sofia Camara</v>
+        <v>Knox</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B17" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Alexander James</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B18" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>almost monday</v>
+        <v>Alexander James</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B19" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Kip Moore</v>
+        <v>almost monday</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>12 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-29</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Santana</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dua Lipa</v>
+        <v>Santana</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Charley - Liar</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B23" t="str">
-        <v>14 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>14 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Charley</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B24" t="str">
-        <v>14 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>14 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>David Guetta</v>
+        <v>Charley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B25" t="str">
-        <v>19 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>19 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Jordana Bryant</v>
+        <v>David Guetta</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>20 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>20 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B27" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-29</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Julia Cole Music</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-29</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>VictorBiliac</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B30" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-29</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-29</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Jungle4eva</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-29</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>DAYTIME TV</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-29</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>13 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-29</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Bruno Mars</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Keith Urban</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Nelly Furtado</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-29</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Lainey Wilson</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Duran Duran</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Nico Santos</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B43" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-29</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Will Linley</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Kylie Minogue</v>
+        <v>Will Linley</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>The Offspring</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>David Gilmour</v>
+        <v>The Offspring</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Scorpions</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Scorpions</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>The Warning</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>paris jackson</v>
+        <v>The Warning</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Minelli</v>
+        <v>paris jackson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B54" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-29</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Maggie Rose</v>
+        <v>Minelli</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B55" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-29</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>David Guetta</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B56" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-29</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>David Guetta</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-29</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Lauv</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B58" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-29</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Icona Pop</v>
+        <v>Lauv</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B59" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-29</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Will Swinton</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B60" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-29</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Dean Lewis</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B61" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-29</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B62" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-29</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Niall Horan</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B63" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-29</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-29</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>RUEL</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-29</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>TINI</v>
+        <v>RUEL</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B66" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-29</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Charli xcx</v>
+        <v>TINI</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B67" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-29</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Dua Lipa</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-29</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Matilda Mann</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-29</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Ella Langley</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-29</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-29</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>kesha</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Holly Humberstone</v>
+        <v>kesha</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-29</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Foo Fighters</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-29</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Analogues</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-29</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Rod Stewart</v>
+        <v>The Analogues</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-29</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Blue October</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-29</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Far Caspian</v>
+        <v>Blue October</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-29</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Kenia Os</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-29</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-29</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B81" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-29</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B82" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-29</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-29</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B84" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-29</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B85" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-29</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-29</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-29</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Evanescence</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Armin van Buuren</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-29</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Madison Cunningham</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B90" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-29</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Johnny Orlando</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-29</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Carver Jones</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-29</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Jazmin bean</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-29</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Baby Queen</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B94" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-29</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Switchfoot</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-29</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Grace Potter</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-29</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-29</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The All-American Rejects</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-29</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Henry Moodie</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-29</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Spacey Jane</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-29</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Megan Moroney</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-29</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Matt Hansen</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>hate that i made you love me</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>petal</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Ariana Grande</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Come Inside</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>petal</v>
       </c>
       <c r="G103" t="str">
-        <v>3:13</v>
+        <v>3:17</v>
       </c>
       <c r="H103" t="str">
-        <v>Paul McCartney</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L103" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Game Time</v>
+        <v>Come Inside</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H104" t="str">
-        <v>Future</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>Game Time - Future</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Game Time</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:36</v>
+        <v>3:26</v>
       </c>
       <c r="H105" t="str">
-        <v>Bossman Dlow</v>
+        <v>Future</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L105" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Aquel diciembre</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:22</v>
+        <v>2:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Young Miko</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L106" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Handle</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Blue Island</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G107" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H107" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Young Miko</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L107" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>The Wave</v>
+        <v>Handle</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sunshine</v>
+        <v>Blue Island</v>
       </c>
       <c r="G108" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H108" t="str">
-        <v>Jungle</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L108" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>STOP</v>
+        <v>The Wave</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G109" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H109" t="str">
-        <v>Bella Kay</v>
+        <v>Jungle</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L109" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>STOP</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Apple Music Sessions</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H110" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L110" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Talk On The Hill</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>The Thread</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G111" t="str">
-        <v>3:27</v>
+        <v>3:08</v>
       </c>
       <c r="H111" t="str">
-        <v>WILLOW</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L111" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No Fear</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Thread</v>
       </c>
       <c r="G112" t="str">
-        <v>3:38</v>
+        <v>3:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Iceage</v>
+        <v>WILLOW</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L112" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>No Fear</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Big Mama</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G113" t="str">
-        <v>3:11</v>
+        <v>3:38</v>
       </c>
       <c r="H113" t="str">
-        <v>Latto</v>
+        <v>Iceage</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L113" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sad Girls</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G114" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H114" t="str">
-        <v>Bebe Rexha</v>
+        <v>Latto</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L114" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:35</v>
+        <v>2:48</v>
       </c>
       <c r="H115" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Rubio</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>La Voz Favorita</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:42</v>
+        <v>3:35</v>
       </c>
       <c r="H116" t="str">
-        <v>Jay Wheeler</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L116" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Pary</v>
+        <v>Rubio</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Con dolor - EP</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G117" t="str">
-        <v>2:52</v>
+        <v>4:42</v>
       </c>
       <c r="H117" t="str">
-        <v>Grupo Frontera</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L117" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Think As You Drunk</v>
+        <v>Pary</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>That's Just Me</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G118" t="str">
-        <v>3:48</v>
+        <v>2:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Riley Green</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L118" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Play Your Games</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Play Your Games - Single</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G119" t="str">
-        <v>3:15</v>
+        <v>3:48</v>
       </c>
       <c r="H119" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Riley Green</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L119" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:47</v>
+        <v>3:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Tom Morello</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:49</v>
+        <v>2:47</v>
       </c>
       <c r="H121" t="str">
-        <v>Blood Orange</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L121" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>minute</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ghosted - EP</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:59</v>
+        <v>4:49</v>
       </c>
       <c r="H122" t="str">
-        <v>Saint Harison</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L122" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>THE LIVING</v>
+        <v>minute</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H123" t="str">
-        <v>Labrinth</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L123" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thug</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thug - Single</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>2:48</v>
       </c>
       <c r="H124" t="str">
-        <v>G Herbo</v>
+        <v>Labrinth</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L124" t="str">
-        <v>Thug - G Herbo</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Clap</v>
+        <v>Thug</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Clap - Single</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:04</v>
+        <v>2:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Polo G</v>
+        <v>G Herbo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L125" t="str">
-        <v>Clap - Polo G</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Clap</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:47</v>
+        <v>2:04</v>
       </c>
       <c r="H126" t="str">
-        <v>YG</v>
+        <v>Polo G</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L126" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G127" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H127" t="str">
-        <v>Jessie Reyez</v>
+        <v>YG</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Joshua Tree</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G128" t="str">
         <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Hans Zimmer</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L128" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Mi Gran Amor</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:37</v>
+        <v>2:50</v>
       </c>
       <c r="H129" t="str">
-        <v>Santana</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L129" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>london</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>stardust - EP</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>3:37</v>
       </c>
       <c r="H130" t="str">
-        <v>Freya Skye</v>
+        <v>Santana</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L130" t="str">
-        <v>london - Freya Skye</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Caution</v>
+        <v>london</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>2:43</v>
+        <v>3:23</v>
       </c>
       <c r="H131" t="str">
-        <v>NMIXX</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L131" t="str">
-        <v>Caution - NMIXX</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Caution</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G132" t="str">
-        <v>3:07</v>
+        <v>2:43</v>
       </c>
       <c r="H132" t="str">
-        <v>aespa</v>
+        <v>NMIXX</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L132" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G133" t="str">
-        <v>2:58</v>
+        <v>3:07</v>
       </c>
       <c r="H133" t="str">
-        <v>Cody Johnson</v>
+        <v>aespa</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L133" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Cheap Thrills</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G134" t="str">
-        <v>2:42</v>
+        <v>2:58</v>
       </c>
       <c r="H134" t="str">
-        <v>Gavin Adcock</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L134" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ME VALE V</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>ACOMODO</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H135" t="str">
-        <v>Tito Double P</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L135" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bug In The Cake</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Be Sweet To Me</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G136" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H136" t="str">
-        <v>Violet Grohl</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L136" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Coil</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Rumspringa</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G137" t="str">
-        <v>3:54</v>
+        <v>2:48</v>
       </c>
       <c r="H137" t="str">
-        <v>ear</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L137" t="str">
-        <v>Coil - ear</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Coil</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G138" t="str">
-        <v>3:30</v>
+        <v>3:54</v>
       </c>
       <c r="H138" t="str">
-        <v>Kneecap</v>
+        <v>ear</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Out of my Head</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:04</v>
+        <v>3:30</v>
       </c>
       <c r="H139" t="str">
-        <v>Cara Delevingne</v>
+        <v>Kneecap</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L139" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Passenger Princess</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:18</v>
+        <v>3:04</v>
       </c>
       <c r="H140" t="str">
-        <v>Perrie</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L140" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Man of the House</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>SE9</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:35</v>
+        <v>3:18</v>
       </c>
       <c r="H141" t="str">
-        <v>Skye Newman</v>
+        <v>Perrie</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L141" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Man of the House</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G142" t="str">
-        <v>2:37</v>
+        <v>2:35</v>
       </c>
       <c r="H142" t="str">
-        <v>MEEK</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L142" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:34</v>
+        <v>2:37</v>
       </c>
       <c r="H143" t="str">
-        <v>ILLENIUM</v>
+        <v>MEEK</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>4:34</v>
       </c>
       <c r="H144" t="str">
-        <v>Lily Allen</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L144" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ABOVE IT</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:45</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Andy Mineo</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L145" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:15</v>
+        <v>1:45</v>
       </c>
       <c r="H146" t="str">
-        <v>Forrest Frank</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L146" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Is It Over Now?</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:39</v>
+        <v>4:15</v>
       </c>
       <c r="H147" t="str">
-        <v>Elderbrook</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L147" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>12 Steps</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>12 Steps - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:11</v>
+        <v>3:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L148" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Over And Over</v>
+        <v>12 Steps</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>It's A Dying Art</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:38</v>
+        <v>3:11</v>
       </c>
       <c r="H149" t="str">
-        <v>Little Big Town</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L149" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>AMAPOLA</v>
+        <v>Over And Over</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ricky y Mau</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G150" t="str">
-        <v>2:22</v>
+        <v>4:38</v>
       </c>
       <c r="H150" t="str">
-        <v>Mau y Ricky</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L150" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Mad About It</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mad About It - Single</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G151" t="str">
-        <v>2:37</v>
+        <v>2:22</v>
       </c>
       <c r="H151" t="str">
-        <v>Dasha</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L151" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Love’s a Gun</v>
+        <v>Mad About It</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:59</v>
+        <v>2:37</v>
       </c>
       <c r="H152" t="str">
-        <v>Daniel Seavey</v>
+        <v>Dasha</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L152" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Long Story Short</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Long Story Short - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H153" t="str">
-        <v>Knox</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L153" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>blue jeans</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>blue jeans - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>2:48</v>
       </c>
       <c r="H154" t="str">
-        <v>Nightly</v>
+        <v>Knox</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L154" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Que Gacho</v>
+        <v>blue jeans</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Que Gacho - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:13</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nightly</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L155" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>same God</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:34</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>Alana Springsteen</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L156" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>emotional swaggage</v>
+        <v>same God</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>IDCASH</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G157" t="str">
-        <v>2:12</v>
+        <v>3:34</v>
       </c>
       <c r="H157" t="str">
-        <v>IDK</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L157" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Baby Driver</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Baby Driver - Single</v>
+        <v>IDCASH</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>2:12</v>
       </c>
       <c r="H158" t="str">
-        <v>070 Shake</v>
+        <v>IDK</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L158" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>More! More! More!</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>REBECCA</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:55</v>
+        <v>3:36</v>
       </c>
       <c r="H159" t="str">
-        <v>Becky Hill</v>
+        <v>070 Shake</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L159" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Young Again</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>EI8HT</v>
+        <v>REBECCA</v>
       </c>
       <c r="G160" t="str">
-        <v>3:36</v>
+        <v>2:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Shinedown</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L160" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>skinny dip</v>
+        <v>Young Again</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>skinny dip - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G161" t="str">
-        <v>3:12</v>
+        <v>3:36</v>
       </c>
       <c r="H161" t="str">
-        <v>almost monday</v>
+        <v>Shinedown</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L161" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>skinny dip</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>girls like girls the album</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:14</v>
+        <v>3:12</v>
       </c>
       <c r="H162" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>almost monday</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L162" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Better Off</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Stages</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G163" t="str">
-        <v>3:16</v>
+        <v>4:14</v>
       </c>
       <c r="H163" t="str">
-        <v>Lauren Alaina</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L163" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Better Off</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Stages</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:16</v>
       </c>
       <c r="H164" t="str">
-        <v>Monaleo</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Lost in translation...</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:30</v>
+        <v>2:48</v>
       </c>
       <c r="H165" t="str">
-        <v>R3HAB</v>
+        <v>Monaleo</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L165" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Call Security</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G166" t="str">
-        <v>3:22</v>
+        <v>3:30</v>
       </c>
       <c r="H166" t="str">
-        <v>Chxrry</v>
+        <v>R3HAB</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L166" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>chaotic</v>
+        <v>Call Security</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>scars to prove it</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G167" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H167" t="str">
-        <v>Hailey Picardi</v>
+        <v>Chxrry</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L167" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Keep It To Yourself</v>
+        <v>chaotic</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G168" t="str">
-        <v>4:17</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>Love Spells</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L168" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Something to Someone</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Something to Someone - Single</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G169" t="str">
-        <v>3:55</v>
+        <v>4:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Max McNown</v>
+        <v>Love Spells</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L169" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Hours: High Noon</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:10</v>
+        <v>3:55</v>
       </c>
       <c r="H170" t="str">
-        <v>Cautious Clay</v>
+        <v>Max McNown</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L170" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Scoreboard</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G171" t="str">
-        <v>3:24</v>
+        <v>2:10</v>
       </c>
       <c r="H171" t="str">
-        <v>Gabriella Rose</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L171" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>High</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:24</v>
       </c>
       <c r="H172" t="str">
-        <v>Nia Smith</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L172" t="str">
-        <v>High - Nia Smith</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Ay Gyal</v>
+        <v>High</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G173" t="str">
-        <v>2:12</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>1Ski OG</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L173" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>always knew</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>always knew - Single</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:25</v>
+        <v>2:12</v>
       </c>
       <c r="H174" t="str">
-        <v>Biscits</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L174" t="str">
-        <v>always knew - Biscits</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cigarette Burns</v>
+        <v>always knew</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:41</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>Corey Kent</v>
+        <v>Biscits</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L175" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Let You Down</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>El Relevo</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G176" t="str">
-        <v>4:14</v>
+        <v>2:41</v>
       </c>
       <c r="H176" t="str">
-        <v>Luis Figueroa</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L176" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Starless</v>
+        <v>Let You Down</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Starless - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G177" t="str">
-        <v>4:32</v>
+        <v>4:14</v>
       </c>
       <c r="H177" t="str">
-        <v>A Perfect Circle</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L177" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking For You</v>
+        <v>Starless</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking For You - Single</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:19</v>
+        <v>4:32</v>
       </c>
       <c r="H178" t="str">
-        <v>Gable Price and Friends</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>FOCUSED</v>
+        <v>Looking For You</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:23</v>
+        <v>3:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Shepherd</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L179" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:23</v>
+        <v>2:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Shepherd</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L180" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>dream state</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>dream state - Single</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L181" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>dream state</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:39</v>
+        <v>4:01</v>
       </c>
       <c r="H182" t="str">
-        <v>Mynolia</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L182" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Inferno</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>5:25</v>
+        <v>3:39</v>
       </c>
       <c r="H183" t="str">
-        <v>Boards of Canada</v>
+        <v>Mynolia</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L183" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G184" t="str">
-        <v>2:34</v>
+        <v>5:25</v>
       </c>
       <c r="H184" t="str">
-        <v>Delroy Edwards</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L184" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>FCUK</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>FCUK - Single</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:22</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>H.LLS</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L185" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Higher</v>
+        <v>FCUK</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:06</v>
+        <v>2:22</v>
       </c>
       <c r="H186" t="str">
-        <v>Francis of Delirium</v>
+        <v>H.LLS</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L186" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>B.U.N</v>
+        <v>Higher</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>B.U.N - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G187" t="str">
-        <v>3:43</v>
+        <v>4:06</v>
       </c>
       <c r="H187" t="str">
-        <v>Roll Deep</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L187" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>B.U.N</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Here Because of Hope</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H188" t="str">
-        <v>Ezra Collective</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L188" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>UNDRA</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G189" t="str">
-        <v>2:49</v>
+        <v>3:22</v>
       </c>
       <c r="H189" t="str">
-        <v>reggie</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L189" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>UNDRA</v>
       </c>
       <c r="G190" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H190" t="str">
-        <v>Johnny Huynh</v>
+        <v>reggie</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L190" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Fallen Angel</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>You Don't Know My Name</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G191" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby J</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L191" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Last Encounter</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G192" t="str">
-        <v>3:04</v>
+        <v>3:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Sofia Camara</v>
+        <v>Baby J</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L192" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>We Fall</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>We Fall - Single</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:01</v>
+        <v>3:04</v>
       </c>
       <c r="H193" t="str">
-        <v>MOIO</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L193" t="str">
-        <v>We Fall - MOIO</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Don't Know Me</v>
+        <v>We Fall</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:50</v>
+        <v>4:01</v>
       </c>
       <c r="H194" t="str">
-        <v>Isabel Dumaa</v>
+        <v>MOIO</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L194" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>House Of Mirrors</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:04</v>
+        <v>3:50</v>
       </c>
       <c r="H195" t="str">
-        <v>All Them Witches</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L195" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Iodine</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Neverending</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G196" t="str">
-        <v>3:40</v>
+        <v>4:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Monolord</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L196" t="str">
-        <v>Iodine - Monolord</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Iodine</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-29</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>...By the Word...</v>
+        <v>Neverending</v>
       </c>
       <c r="G197" t="str">
-        <v>5:01</v>
+        <v>3:40</v>
       </c>
       <c r="H197" t="str">
-        <v>Trelldom</v>
+        <v>Monolord</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L197" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>I Speak Forgotten Voices</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>...By the Word...</v>
+      </c>
+      <c r="G198" t="str">
+        <v>5:01</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Trelldom</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+      </c>
+      <c r="L198" t="str">
+        <v>I Speak Forgotten Voices - Trelldom</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-05-29</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:45</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Flotsam and Jetsam</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אור קודאי – פירורים</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-29</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a7%d7%95%d7%93%d7%90%d7%99-%d7%a4%d7%99%d7%a8%d7%95%d7%a8%d7%99%d7%9d/</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אור קודאי שר בלדה מלנכולית שנשענת פחות על עלילה ויותר על תחושה – תחושת ריקנות אחרי אהבה שנשחקה עד שלא נותר ממנה כמעט דבר. הדימוי "פירורים" מבטא לא שברון לב דרמטי, אלא שאריות. של משהו שהיה פעם שלם, חם ומזין,</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Dua Lipa</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אור קודאי – פירורים</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-29</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dua Lipa</v>
+        <v>Dagny</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-29</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dagny</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>9 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>9 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Dogpark</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Dogpark</v>
+        <v>elijah woods</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>elijah woods</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-29</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Lauren Alaina</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Lauren Sanderson</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>NIGHTLY</v>
+        <v>Dasha</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B12" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Dasha</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Ariana Grande</v>
+        <v>Max McNown</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Max McNown</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Bebe Rexha</v>
+        <v>Knox</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B16" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Knox</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B17" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Sofia Camara</v>
+        <v>Alexander James</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Alexander James</v>
+        <v>almost monday</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B19" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>almost monday</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Kip Moore</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>12 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-29</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>12 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Santana</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B22" t="str">
-        <v>16 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>16 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Santana</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B23" t="str">
-        <v>17 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>17 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dua Lipa</v>
+        <v>Charley</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Charley - Liar</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
-        <v>18 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>18 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Charley</v>
+        <v>David Guetta</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>David Guetta</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B26" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Jordana Bryant</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Julia Cole Music</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-29</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>VictorBiliac</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-29</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-29</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Jungle4eva</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-29</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>DAYTIME TV</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B34" t="str">
-        <v>2 weeks ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-29</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 weeks ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Bruno Mars</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Keith Urban</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-29</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Nelly Furtado</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B39" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-29</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Lainey Wilson</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Duran Duran</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Nico Santos</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Will Linley</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-29</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Will Linley</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-29</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Kylie Minogue</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-29</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Billy Raffoul</v>
+        <v>The Offspring</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B47" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-29</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>The Offspring</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B48" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-29</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>David Gilmour</v>
+        <v>Scorpions</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-29</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Scorpions</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-29</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B51" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-29</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>The Warning</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B52" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-29</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>The Warning</v>
+        <v>paris jackson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B53" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-29</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>paris jackson</v>
+        <v>Minelli</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B54" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-29</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Minelli</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B55" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-29</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Maggie Rose</v>
+        <v>David Guetta</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-29</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>David Guetta</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B57" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-29</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Lauv</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B58" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-29</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Lauv</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B59" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-29</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Icona Pop</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B60" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-29</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Will Swinton</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B61" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-29</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Dean Lewis</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-29</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-29</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Niall Horan</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-29</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>RUEL</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B65" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-29</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>RUEL</v>
+        <v>TINI</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-29</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>TINI</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B67" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Charli xcx</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-29</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Dua Lipa</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-29</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Matilda Mann</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-29</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Ella Langley</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Nothing But Thieves</v>
+        <v>kesha</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-29</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>kesha</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-29</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Holly Humberstone</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-29</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Foo Fighters</v>
+        <v>The Analogues</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-29</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>The Analogues</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-29</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Rod Stewart</v>
+        <v>Blue October</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-29</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Blue October</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-29</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Far Caspian</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-29</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Kenia Os</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-29</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B81" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-29</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B82" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-29</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-29</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B84" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-29</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B85" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-29</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-29</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Evanescence</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-29</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Evanescence</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B89" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-29</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Armin van Buuren</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-29</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Madison Cunningham</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-29</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Johnny Orlando</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-29</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Carver Jones</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-29</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Jazmin bean</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-29</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Baby Queen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-29</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Switchfoot</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-29</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Grace Potter</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-29</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-29</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>The All-American Rejects</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-29</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Henry Moodie</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-29</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Spacey Jane</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-29</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Megan Moroney</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>petal</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H102" t="str">
-        <v>Matt Hansen</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L102" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>hate that i made you love me</v>
+        <v>Come Inside</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>petal</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v>3:13</v>
       </c>
       <c r="H103" t="str">
-        <v>Ariana Grande</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L103" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Come Inside</v>
+        <v>Game Time</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>Future</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L104" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Game Time</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:26</v>
+        <v>2:36</v>
       </c>
       <c r="H105" t="str">
-        <v>Future</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L105" t="str">
-        <v>Game Time - Future</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G106" t="str">
-        <v>2:36</v>
+        <v>3:22</v>
       </c>
       <c r="H106" t="str">
-        <v>Bossman Dlow</v>
+        <v>Young Miko</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L106" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Aquel diciembre</v>
+        <v>Handle</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Blue Island</v>
       </c>
       <c r="G107" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H107" t="str">
-        <v>Young Miko</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L107" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Handle</v>
+        <v>The Wave</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Blue Island</v>
+        <v>Sunshine</v>
       </c>
       <c r="G108" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H108" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Jungle</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L108" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>The Wave</v>
+        <v>STOP</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sunshine</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:22</v>
+        <v>2:56</v>
       </c>
       <c r="H109" t="str">
-        <v>Jungle</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L109" t="str">
-        <v>The Wave - Jungle</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>STOP</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G110" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H110" t="str">
-        <v>Bella Kay</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L110" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Apple Music Sessions</v>
+        <v>The Thread</v>
       </c>
       <c r="G111" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H111" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>WILLOW</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L111" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Talk On The Hill</v>
+        <v>No Fear</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>The Thread</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G112" t="str">
-        <v>3:27</v>
+        <v>3:38</v>
       </c>
       <c r="H112" t="str">
-        <v>WILLOW</v>
+        <v>Iceage</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L112" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No Fear</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Big Mama</v>
       </c>
       <c r="G113" t="str">
-        <v>3:38</v>
+        <v>3:11</v>
       </c>
       <c r="H113" t="str">
-        <v>Iceage</v>
+        <v>Latto</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L113" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Big Mama</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H114" t="str">
-        <v>Latto</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L114" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Sad Girls</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H115" t="str">
-        <v>Bebe Rexha</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L115" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Rubio</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G116" t="str">
-        <v>3:35</v>
+        <v>4:42</v>
       </c>
       <c r="H116" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Rubio</v>
+        <v>Pary</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>La Voz Favorita</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>4:42</v>
+        <v>2:52</v>
       </c>
       <c r="H117" t="str">
-        <v>Jay Wheeler</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L117" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Pary</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Con dolor - EP</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G118" t="str">
-        <v>2:52</v>
+        <v>3:48</v>
       </c>
       <c r="H118" t="str">
-        <v>Grupo Frontera</v>
+        <v>Riley Green</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L118" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Think As You Drunk</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>That's Just Me</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:48</v>
+        <v>3:15</v>
       </c>
       <c r="H119" t="str">
-        <v>Riley Green</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L119" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Play Your Games</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Play Your Games - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:15</v>
+        <v>2:47</v>
       </c>
       <c r="H120" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L120" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:47</v>
+        <v>4:49</v>
       </c>
       <c r="H121" t="str">
-        <v>Tom Morello</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>minute</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>4:49</v>
+        <v>2:59</v>
       </c>
       <c r="H122" t="str">
-        <v>Blood Orange</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L122" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>minute</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ghosted - EP</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>2:59</v>
+        <v>2:48</v>
       </c>
       <c r="H123" t="str">
-        <v>Saint Harison</v>
+        <v>Labrinth</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L123" t="str">
-        <v>minute - Saint Harison</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>THE LIVING</v>
+        <v>Thug</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:48</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Labrinth</v>
+        <v>G Herbo</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L124" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thug</v>
+        <v>Clap</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Thug - Single</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:25</v>
+        <v>2:04</v>
       </c>
       <c r="H125" t="str">
-        <v>G Herbo</v>
+        <v>Polo G</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L125" t="str">
-        <v>Thug - G Herbo</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Clap</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Clap - Single</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G126" t="str">
-        <v>2:04</v>
+        <v>2:47</v>
       </c>
       <c r="H126" t="str">
-        <v>Polo G</v>
+        <v>YG</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L126" t="str">
-        <v>Clap - Polo G</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>GANG BIZNESS</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G127" t="str">
-        <v>2:47</v>
+        <v>2:50</v>
       </c>
       <c r="H127" t="str">
-        <v>YG</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L127" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G128" t="str">
         <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Jessie Reyez</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L128" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Joshua Tree</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:50</v>
+        <v>3:37</v>
       </c>
       <c r="H129" t="str">
-        <v>Hans Zimmer</v>
+        <v>Santana</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L129" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Mi Gran Amor</v>
+        <v>london</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:37</v>
+        <v>3:23</v>
       </c>
       <c r="H130" t="str">
-        <v>Santana</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L130" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>london</v>
+        <v>Caution</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>stardust - EP</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G131" t="str">
-        <v>3:23</v>
+        <v>2:43</v>
       </c>
       <c r="H131" t="str">
-        <v>Freya Skye</v>
+        <v>NMIXX</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L131" t="str">
-        <v>london - Freya Skye</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Caution</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G132" t="str">
-        <v>2:43</v>
+        <v>3:07</v>
       </c>
       <c r="H132" t="str">
-        <v>NMIXX</v>
+        <v>aespa</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L132" t="str">
-        <v>Caution - NMIXX</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G133" t="str">
-        <v>3:07</v>
+        <v>2:58</v>
       </c>
       <c r="H133" t="str">
-        <v>aespa</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L133" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:58</v>
+        <v>2:42</v>
       </c>
       <c r="H134" t="str">
-        <v>Cody Johnson</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L134" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Cheap Thrills</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G135" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H135" t="str">
-        <v>Gavin Adcock</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L135" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ME VALE V</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>ACOMODO</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G136" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H136" t="str">
-        <v>Tito Double P</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L136" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Bug In The Cake</v>
+        <v>Coil</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G137" t="str">
-        <v>2:48</v>
+        <v>3:54</v>
       </c>
       <c r="H137" t="str">
-        <v>Violet Grohl</v>
+        <v>ear</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L137" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Coil</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Rumspringa</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:54</v>
+        <v>3:30</v>
       </c>
       <c r="H138" t="str">
-        <v>ear</v>
+        <v>Kneecap</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L138" t="str">
-        <v>Coil - ear</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:30</v>
+        <v>3:04</v>
       </c>
       <c r="H139" t="str">
-        <v>Kneecap</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Out of my Head</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:04</v>
+        <v>3:18</v>
       </c>
       <c r="H140" t="str">
-        <v>Cara Delevingne</v>
+        <v>Perrie</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L140" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Passenger Princess</v>
+        <v>Man of the House</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G141" t="str">
-        <v>3:18</v>
+        <v>2:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Perrie</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L141" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Man of the House</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>SE9</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:35</v>
+        <v>2:37</v>
       </c>
       <c r="H142" t="str">
-        <v>Skye Newman</v>
+        <v>MEEK</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L142" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:37</v>
+        <v>4:34</v>
       </c>
       <c r="H143" t="str">
-        <v>MEEK</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L143" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>4:34</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>ILLENIUM</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L144" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>1:45</v>
       </c>
       <c r="H145" t="str">
-        <v>Lily Allen</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L145" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ABOVE IT</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:45</v>
+        <v>4:15</v>
       </c>
       <c r="H146" t="str">
-        <v>Andy Mineo</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L146" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:15</v>
+        <v>3:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Forrest Frank</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L147" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Is It Over Now?</v>
+        <v>12 Steps</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:39</v>
+        <v>3:11</v>
       </c>
       <c r="H148" t="str">
-        <v>Elderbrook</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L148" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>12 Steps</v>
+        <v>Over And Over</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>12 Steps - Single</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G149" t="str">
-        <v>3:11</v>
+        <v>4:38</v>
       </c>
       <c r="H149" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L149" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Over And Over</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>It's A Dying Art</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G150" t="str">
-        <v>4:38</v>
+        <v>2:22</v>
       </c>
       <c r="H150" t="str">
-        <v>Little Big Town</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L150" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>AMAPOLA</v>
+        <v>Mad About It</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ricky y Mau</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:22</v>
+        <v>2:37</v>
       </c>
       <c r="H151" t="str">
-        <v>Mau y Ricky</v>
+        <v>Dasha</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L151" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mad About It</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mad About It - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:37</v>
+        <v>2:59</v>
       </c>
       <c r="H152" t="str">
-        <v>Dasha</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L152" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Love’s a Gun</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:59</v>
+        <v>2:48</v>
       </c>
       <c r="H153" t="str">
-        <v>Daniel Seavey</v>
+        <v>Knox</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L153" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Long Story Short</v>
+        <v>blue jeans</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Long Story Short - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:48</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Knox</v>
+        <v>Nightly</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L154" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>blue jeans</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>blue jeans - Single</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>3:13</v>
       </c>
       <c r="H155" t="str">
-        <v>Nightly</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L155" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Que Gacho</v>
+        <v>same God</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Que Gacho - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G156" t="str">
-        <v>3:13</v>
+        <v>3:34</v>
       </c>
       <c r="H156" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L156" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>same God</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>IDCASH</v>
       </c>
       <c r="G157" t="str">
-        <v>3:34</v>
+        <v>2:12</v>
       </c>
       <c r="H157" t="str">
-        <v>Alana Springsteen</v>
+        <v>IDK</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L157" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>emotional swaggage</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>IDCASH</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:12</v>
+        <v>3:36</v>
       </c>
       <c r="H158" t="str">
-        <v>IDK</v>
+        <v>070 Shake</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L158" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Baby Driver</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Baby Driver - Single</v>
+        <v>REBECCA</v>
       </c>
       <c r="G159" t="str">
-        <v>3:36</v>
+        <v>2:55</v>
       </c>
       <c r="H159" t="str">
-        <v>070 Shake</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L159" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>More! More! More!</v>
+        <v>Young Again</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>REBECCA</v>
+        <v>EI8HT</v>
       </c>
       <c r="G160" t="str">
-        <v>2:55</v>
+        <v>3:36</v>
       </c>
       <c r="H160" t="str">
-        <v>Becky Hill</v>
+        <v>Shinedown</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L160" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Young Again</v>
+        <v>skinny dip</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>EI8HT</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:36</v>
+        <v>3:12</v>
       </c>
       <c r="H161" t="str">
-        <v>Shinedown</v>
+        <v>almost monday</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L161" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>skinny dip</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>skinny dip - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G162" t="str">
-        <v>3:12</v>
+        <v>4:14</v>
       </c>
       <c r="H162" t="str">
-        <v>almost monday</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L162" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>Better Off</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>girls like girls the album</v>
+        <v>Stages</v>
       </c>
       <c r="G163" t="str">
-        <v>4:14</v>
+        <v>3:16</v>
       </c>
       <c r="H163" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L163" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Better Off</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Stages</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:16</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Lauren Alaina</v>
+        <v>Monaleo</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L164" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G165" t="str">
-        <v>2:48</v>
+        <v>3:30</v>
       </c>
       <c r="H165" t="str">
-        <v>Monaleo</v>
+        <v>R3HAB</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Lost in translation...</v>
+        <v>Call Security</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Dream inside a dream…</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G166" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H166" t="str">
-        <v>R3HAB</v>
+        <v>Chxrry</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L166" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Call Security</v>
+        <v>chaotic</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G167" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H167" t="str">
-        <v>Chxrry</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L167" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>chaotic</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>scars to prove it</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>4:17</v>
       </c>
       <c r="H168" t="str">
-        <v>Hailey Picardi</v>
+        <v>Love Spells</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L168" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Keep It To Yourself</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:17</v>
+        <v>3:55</v>
       </c>
       <c r="H169" t="str">
-        <v>Love Spells</v>
+        <v>Max McNown</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L169" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Something to Someone</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Something to Someone - Single</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G170" t="str">
-        <v>3:55</v>
+        <v>2:10</v>
       </c>
       <c r="H170" t="str">
-        <v>Max McNown</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L170" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Hours: High Noon</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G171" t="str">
-        <v>2:10</v>
+        <v>3:24</v>
       </c>
       <c r="H171" t="str">
-        <v>Cautious Clay</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L171" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Scoreboard</v>
+        <v>High</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G172" t="str">
-        <v>3:24</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>Gabriella Rose</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L172" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>High</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>2:12</v>
       </c>
       <c r="H173" t="str">
-        <v>Nia Smith</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L173" t="str">
-        <v>High - Nia Smith</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ay Gyal</v>
+        <v>always knew</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:12</v>
+        <v>3:25</v>
       </c>
       <c r="H174" t="str">
-        <v>1Ski OG</v>
+        <v>Biscits</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L174" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>always knew</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>always knew - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G175" t="str">
-        <v>3:25</v>
+        <v>2:41</v>
       </c>
       <c r="H175" t="str">
-        <v>Biscits</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L175" t="str">
-        <v>always knew - Biscits</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Cigarette Burns</v>
+        <v>Let You Down</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>El Relevo</v>
       </c>
       <c r="G176" t="str">
-        <v>2:41</v>
+        <v>4:14</v>
       </c>
       <c r="H176" t="str">
-        <v>Corey Kent</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L176" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Let You Down</v>
+        <v>Starless</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>El Relevo</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:14</v>
+        <v>4:32</v>
       </c>
       <c r="H177" t="str">
-        <v>Luis Figueroa</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L177" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Starless</v>
+        <v>Looking For You</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Starless - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:32</v>
+        <v>3:19</v>
       </c>
       <c r="H178" t="str">
-        <v>A Perfect Circle</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L178" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Looking For You</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Looking For You - Single</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:19</v>
+        <v>2:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Shepherd</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L179" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>FOCUSED</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:23</v>
+        <v>3:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Shepherd</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L180" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>dream state</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H181" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L181" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>dream state</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>dream state - Single</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:01</v>
+        <v>3:39</v>
       </c>
       <c r="H182" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Mynolia</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L182" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G183" t="str">
-        <v>3:39</v>
+        <v>5:25</v>
       </c>
       <c r="H183" t="str">
-        <v>Mynolia</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L183" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Inferno</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>5:25</v>
+        <v>2:34</v>
       </c>
       <c r="H184" t="str">
-        <v>Boards of Canada</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L184" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>FCUK</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:34</v>
+        <v>2:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Delroy Edwards</v>
+        <v>H.LLS</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L185" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>FCUK</v>
+        <v>Higher</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>FCUK - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G186" t="str">
-        <v>2:22</v>
+        <v>4:06</v>
       </c>
       <c r="H186" t="str">
-        <v>H.LLS</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L186" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Higher</v>
+        <v>B.U.N</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:06</v>
+        <v>3:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Francis of Delirium</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L187" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>B.U.N</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>B.U.N - Single</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G188" t="str">
-        <v>3:43</v>
+        <v>3:22</v>
       </c>
       <c r="H188" t="str">
-        <v>Roll Deep</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L188" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Here Because of Hope</v>
+        <v>UNDRA</v>
       </c>
       <c r="G189" t="str">
-        <v>3:22</v>
+        <v>2:49</v>
       </c>
       <c r="H189" t="str">
-        <v>Ezra Collective</v>
+        <v>reggie</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L189" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>UNDRA</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G190" t="str">
-        <v>2:49</v>
+        <v>2:54</v>
       </c>
       <c r="H190" t="str">
-        <v>reggie</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L190" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G191" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Johnny Huynh</v>
+        <v>Baby J</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L191" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Fallen Angel</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>You Don't Know My Name</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Baby J</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L192" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Last Encounter</v>
+        <v>We Fall</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:04</v>
+        <v>4:01</v>
       </c>
       <c r="H193" t="str">
-        <v>Sofia Camara</v>
+        <v>MOIO</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L193" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>We Fall</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>We Fall - Single</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:01</v>
+        <v>3:50</v>
       </c>
       <c r="H194" t="str">
-        <v>MOIO</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L194" t="str">
-        <v>We Fall - MOIO</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>You Don't Know Me</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G195" t="str">
-        <v>3:50</v>
+        <v>4:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Isabel Dumaa</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L195" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>Iodine</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>House Of Mirrors</v>
+        <v>Neverending</v>
       </c>
       <c r="G196" t="str">
-        <v>4:04</v>
+        <v>3:40</v>
       </c>
       <c r="H196" t="str">
-        <v>All Them Witches</v>
+        <v>Monolord</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L196" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Iodine</v>
+        <v>I Speak Forgotten Voices</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Neverending</v>
+        <v>...By the Word...</v>
       </c>
       <c r="G197" t="str">
-        <v>3:40</v>
+        <v>5:01</v>
       </c>
       <c r="H197" t="str">
-        <v>Monolord</v>
+        <v>Trelldom</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
       </c>
       <c r="L197" t="str">
-        <v>Iodine - Monolord</v>
+        <v>I Speak Forgotten Voices - Trelldom</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-29</v>
@@ -7899,68 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>...By the Word...</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="G198" t="str">
-        <v>5:01</v>
+        <v>4:45</v>
       </c>
       <c r="H198" t="str">
-        <v>Trelldom</v>
+        <v>Flotsam and Jetsam</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
       <c r="L198" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-05-29</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="G199" t="str">
-        <v>4:45</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Flotsam and Jetsam</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
-      </c>
-      <c r="L199" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B12" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B16" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B17" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B19" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B22" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Charley - Liar</v>
       </c>
       <c r="B23" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>

--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B12" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B16" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B17" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B19" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B22" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Charley - Liar</v>
       </c>
       <c r="B23" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B65" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E198" t="str">
         <v/>

--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B12" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B16" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B17" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B19" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>

--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>איתי עברון – בא מלמטה</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%a2%d7%91%d7%a8%d7%95%d7%9f-%d7%91%d7%90-%d7%9e%d7%9c%d7%9e%d7%98%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-30</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>"בא מלמטה" של איתי עברון  הוא שיר רוק קברטי-תיאטרלי שמציג דיוקן עצמי חסר מעצורים של אמן צעיר הנאבק בין הצורך להתקבל לבין הדחף להיות נאמן לאש הפנימית שלו. זהו שיר על זהות, מעמד, שאפתנות ועל הסירוב להתנצל על מי שאתה.</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Dua Lipa</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>איתי עברון – בא מלמטה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-30</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dagny</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-30</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Dagny</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-30</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-30</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Dogpark</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-30</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>elijah woods</v>
+        <v>Dogpark</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-30</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Lauren Alaina</v>
+        <v>elijah woods</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-30</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-30</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>NIGHTLY</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-30</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Dasha</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-30</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ariana Grande</v>
+        <v>Dasha</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-30</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Max McNown</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-30</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v>Max McNown</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-30</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Knox</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-30</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Sofia Camara</v>
+        <v>Knox</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-30</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Alexander James</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-30</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>almost monday</v>
+        <v>Alexander James</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-30</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Kip Moore</v>
+        <v>almost monday</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-30</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-30</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Santana</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-30</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dua Lipa</v>
+        <v>Santana</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Charley - Liar</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-30</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Charley</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-30</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>David Guetta</v>
+        <v>Charley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-30</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Jordana Bryant</v>
+        <v>David Guetta</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-30</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-30</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-30</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Julia Cole Music</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-30</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>VictorBiliac</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-30</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-30</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Jungle4eva</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-30</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>DAYTIME TV</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 weeks ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-30</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 weeks ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-30</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Bruno Mars</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-30</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Keith Urban</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-30</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Nelly Furtado</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-30</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-30</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-30</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Lainey Wilson</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-30</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Duran Duran</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-30</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Nico Santos</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-30</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-30</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Will Linley</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-30</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Kylie Minogue</v>
+        <v>Will Linley</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-30</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-30</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>The Offspring</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-30</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>David Gilmour</v>
+        <v>The Offspring</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-30</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Scorpions</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-30</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Scorpions</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-30</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-30</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>The Warning</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-30</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>paris jackson</v>
+        <v>The Warning</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-30</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Minelli</v>
+        <v>paris jackson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-30</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Maggie Rose</v>
+        <v>Minelli</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-30</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>David Guetta</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-30</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>David Guetta</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-30</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Lauv</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-30</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Icona Pop</v>
+        <v>Lauv</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-30</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Will Swinton</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-30</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Dean Lewis</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-30</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-30</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Niall Horan</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-30</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-30</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>RUEL</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-30</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>TINI</v>
+        <v>RUEL</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-30</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Charli xcx</v>
+        <v>TINI</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-30</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Dua Lipa</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-30</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Matilda Mann</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-30</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Ella Langley</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-30</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-30</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>kesha</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-30</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Holly Humberstone</v>
+        <v>kesha</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-30</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Foo Fighters</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-30</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Analogues</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-30</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Rod Stewart</v>
+        <v>The Analogues</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-30</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Blue October</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-30</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Far Caspian</v>
+        <v>Blue October</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-30</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Kenia Os</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-30</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-30</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-30</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-30</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-30</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-30</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-30</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-30</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-30</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Evanescence</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-30</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Armin van Buuren</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-30</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Madison Cunningham</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-30</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Johnny Orlando</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-30</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Carver Jones</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-30</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Jazmin bean</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-30</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Baby Queen</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-30</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Switchfoot</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-30</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Grace Potter</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-30</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-30</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The All-American Rejects</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-30</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Henry Moodie</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-30</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Spacey Jane</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-30</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Megan Moroney</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-30</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Matt Hansen</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>hate that i made you love me</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-30</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>petal</v>
+        <v>2w ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Ariana Grande</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Come Inside</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-30</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>petal</v>
       </c>
       <c r="G103" t="str">
-        <v>3:13</v>
+        <v>3:17</v>
       </c>
       <c r="H103" t="str">
-        <v>Paul McCartney</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L103" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Game Time</v>
+        <v>Come Inside</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-30</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H104" t="str">
-        <v>Future</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>Game Time - Future</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Game Time</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-30</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:36</v>
+        <v>3:26</v>
       </c>
       <c r="H105" t="str">
-        <v>Bossman Dlow</v>
+        <v>Future</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L105" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Aquel diciembre</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-30</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:22</v>
+        <v>2:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Young Miko</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L106" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Handle</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-30</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Blue Island</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G107" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H107" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Young Miko</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L107" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>The Wave</v>
+        <v>Handle</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-30</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sunshine</v>
+        <v>Blue Island</v>
       </c>
       <c r="G108" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H108" t="str">
-        <v>Jungle</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L108" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>STOP</v>
+        <v>The Wave</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-30</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G109" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H109" t="str">
-        <v>Bella Kay</v>
+        <v>Jungle</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L109" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>STOP</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-30</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Apple Music Sessions</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H110" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L110" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Talk On The Hill</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-30</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>The Thread</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G111" t="str">
-        <v>3:27</v>
+        <v>3:08</v>
       </c>
       <c r="H111" t="str">
-        <v>WILLOW</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L111" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No Fear</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-30</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Thread</v>
       </c>
       <c r="G112" t="str">
-        <v>3:38</v>
+        <v>3:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Iceage</v>
+        <v>WILLOW</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L112" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>No Fear</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-30</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Big Mama</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G113" t="str">
-        <v>3:11</v>
+        <v>3:38</v>
       </c>
       <c r="H113" t="str">
-        <v>Latto</v>
+        <v>Iceage</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L113" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sad Girls</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-30</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G114" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H114" t="str">
-        <v>Bebe Rexha</v>
+        <v>Latto</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L114" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-30</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:35</v>
+        <v>2:48</v>
       </c>
       <c r="H115" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Rubio</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>La Voz Favorita</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:42</v>
+        <v>3:35</v>
       </c>
       <c r="H116" t="str">
-        <v>Jay Wheeler</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L116" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Pary</v>
+        <v>Rubio</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Con dolor - EP</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G117" t="str">
-        <v>2:52</v>
+        <v>4:42</v>
       </c>
       <c r="H117" t="str">
-        <v>Grupo Frontera</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L117" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Think As You Drunk</v>
+        <v>Pary</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>That's Just Me</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G118" t="str">
-        <v>3:48</v>
+        <v>2:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Riley Green</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L118" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Play Your Games</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Play Your Games - Single</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G119" t="str">
-        <v>3:15</v>
+        <v>3:48</v>
       </c>
       <c r="H119" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Riley Green</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L119" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:47</v>
+        <v>3:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Tom Morello</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:49</v>
+        <v>2:47</v>
       </c>
       <c r="H121" t="str">
-        <v>Blood Orange</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L121" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>minute</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ghosted - EP</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:59</v>
+        <v>4:49</v>
       </c>
       <c r="H122" t="str">
-        <v>Saint Harison</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L122" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>THE LIVING</v>
+        <v>minute</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H123" t="str">
-        <v>Labrinth</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L123" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thug</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thug - Single</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>2:48</v>
       </c>
       <c r="H124" t="str">
-        <v>G Herbo</v>
+        <v>Labrinth</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L124" t="str">
-        <v>Thug - G Herbo</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Clap</v>
+        <v>Thug</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Clap - Single</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:04</v>
+        <v>2:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Polo G</v>
+        <v>G Herbo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L125" t="str">
-        <v>Clap - Polo G</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Clap</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:47</v>
+        <v>2:04</v>
       </c>
       <c r="H126" t="str">
-        <v>YG</v>
+        <v>Polo G</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L126" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G127" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H127" t="str">
-        <v>Jessie Reyez</v>
+        <v>YG</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Joshua Tree</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G128" t="str">
         <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Hans Zimmer</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L128" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Mi Gran Amor</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:37</v>
+        <v>2:50</v>
       </c>
       <c r="H129" t="str">
-        <v>Santana</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L129" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>london</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>stardust - EP</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>3:37</v>
       </c>
       <c r="H130" t="str">
-        <v>Freya Skye</v>
+        <v>Santana</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L130" t="str">
-        <v>london - Freya Skye</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Caution</v>
+        <v>london</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>2:43</v>
+        <v>3:23</v>
       </c>
       <c r="H131" t="str">
-        <v>NMIXX</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L131" t="str">
-        <v>Caution - NMIXX</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Caution</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G132" t="str">
-        <v>3:07</v>
+        <v>2:43</v>
       </c>
       <c r="H132" t="str">
-        <v>aespa</v>
+        <v>NMIXX</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L132" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G133" t="str">
-        <v>2:58</v>
+        <v>3:07</v>
       </c>
       <c r="H133" t="str">
-        <v>Cody Johnson</v>
+        <v>aespa</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L133" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Cheap Thrills</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G134" t="str">
-        <v>2:42</v>
+        <v>2:58</v>
       </c>
       <c r="H134" t="str">
-        <v>Gavin Adcock</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L134" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ME VALE V</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>ACOMODO</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H135" t="str">
-        <v>Tito Double P</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L135" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bug In The Cake</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Be Sweet To Me</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G136" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H136" t="str">
-        <v>Violet Grohl</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L136" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Coil</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Rumspringa</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G137" t="str">
-        <v>3:54</v>
+        <v>2:48</v>
       </c>
       <c r="H137" t="str">
-        <v>ear</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L137" t="str">
-        <v>Coil - ear</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Coil</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G138" t="str">
-        <v>3:30</v>
+        <v>3:54</v>
       </c>
       <c r="H138" t="str">
-        <v>Kneecap</v>
+        <v>ear</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Out of my Head</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:04</v>
+        <v>3:30</v>
       </c>
       <c r="H139" t="str">
-        <v>Cara Delevingne</v>
+        <v>Kneecap</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L139" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Passenger Princess</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:18</v>
+        <v>3:04</v>
       </c>
       <c r="H140" t="str">
-        <v>Perrie</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L140" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Man of the House</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>SE9</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:35</v>
+        <v>3:18</v>
       </c>
       <c r="H141" t="str">
-        <v>Skye Newman</v>
+        <v>Perrie</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L141" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Man of the House</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G142" t="str">
-        <v>2:37</v>
+        <v>2:35</v>
       </c>
       <c r="H142" t="str">
-        <v>MEEK</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L142" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:34</v>
+        <v>2:37</v>
       </c>
       <c r="H143" t="str">
-        <v>ILLENIUM</v>
+        <v>MEEK</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>4:34</v>
       </c>
       <c r="H144" t="str">
-        <v>Lily Allen</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L144" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ABOVE IT</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:45</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Andy Mineo</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L145" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:15</v>
+        <v>1:45</v>
       </c>
       <c r="H146" t="str">
-        <v>Forrest Frank</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L146" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Is It Over Now?</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:39</v>
+        <v>4:15</v>
       </c>
       <c r="H147" t="str">
-        <v>Elderbrook</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L147" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>12 Steps</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>12 Steps - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:11</v>
+        <v>3:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L148" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Over And Over</v>
+        <v>12 Steps</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>It's A Dying Art</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:38</v>
+        <v>3:11</v>
       </c>
       <c r="H149" t="str">
-        <v>Little Big Town</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L149" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>AMAPOLA</v>
+        <v>Over And Over</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ricky y Mau</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G150" t="str">
-        <v>2:22</v>
+        <v>4:38</v>
       </c>
       <c r="H150" t="str">
-        <v>Mau y Ricky</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L150" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Mad About It</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mad About It - Single</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G151" t="str">
-        <v>2:37</v>
+        <v>2:22</v>
       </c>
       <c r="H151" t="str">
-        <v>Dasha</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L151" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Love’s a Gun</v>
+        <v>Mad About It</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:59</v>
+        <v>2:37</v>
       </c>
       <c r="H152" t="str">
-        <v>Daniel Seavey</v>
+        <v>Dasha</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L152" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Long Story Short</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Long Story Short - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H153" t="str">
-        <v>Knox</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L153" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>blue jeans</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>blue jeans - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>2:48</v>
       </c>
       <c r="H154" t="str">
-        <v>Nightly</v>
+        <v>Knox</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L154" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Que Gacho</v>
+        <v>blue jeans</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Que Gacho - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:13</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nightly</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L155" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>same God</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:34</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>Alana Springsteen</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L156" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>emotional swaggage</v>
+        <v>same God</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>IDCASH</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G157" t="str">
-        <v>2:12</v>
+        <v>3:34</v>
       </c>
       <c r="H157" t="str">
-        <v>IDK</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L157" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Baby Driver</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Baby Driver - Single</v>
+        <v>IDCASH</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>2:12</v>
       </c>
       <c r="H158" t="str">
-        <v>070 Shake</v>
+        <v>IDK</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L158" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>More! More! More!</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>REBECCA</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:55</v>
+        <v>3:36</v>
       </c>
       <c r="H159" t="str">
-        <v>Becky Hill</v>
+        <v>070 Shake</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L159" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Young Again</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>EI8HT</v>
+        <v>REBECCA</v>
       </c>
       <c r="G160" t="str">
-        <v>3:36</v>
+        <v>2:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Shinedown</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L160" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>skinny dip</v>
+        <v>Young Again</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>skinny dip - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G161" t="str">
-        <v>3:12</v>
+        <v>3:36</v>
       </c>
       <c r="H161" t="str">
-        <v>almost monday</v>
+        <v>Shinedown</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L161" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>skinny dip</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>girls like girls the album</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:14</v>
+        <v>3:12</v>
       </c>
       <c r="H162" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>almost monday</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L162" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Better Off</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Stages</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G163" t="str">
-        <v>3:16</v>
+        <v>4:14</v>
       </c>
       <c r="H163" t="str">
-        <v>Lauren Alaina</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L163" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Better Off</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Stages</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:16</v>
       </c>
       <c r="H164" t="str">
-        <v>Monaleo</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Lost in translation...</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:30</v>
+        <v>2:48</v>
       </c>
       <c r="H165" t="str">
-        <v>R3HAB</v>
+        <v>Monaleo</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L165" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Call Security</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G166" t="str">
-        <v>3:22</v>
+        <v>3:30</v>
       </c>
       <c r="H166" t="str">
-        <v>Chxrry</v>
+        <v>R3HAB</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L166" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>chaotic</v>
+        <v>Call Security</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>scars to prove it</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G167" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H167" t="str">
-        <v>Hailey Picardi</v>
+        <v>Chxrry</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L167" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Keep It To Yourself</v>
+        <v>chaotic</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G168" t="str">
-        <v>4:17</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>Love Spells</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L168" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Something to Someone</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Something to Someone - Single</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G169" t="str">
-        <v>3:55</v>
+        <v>4:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Max McNown</v>
+        <v>Love Spells</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L169" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Hours: High Noon</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:10</v>
+        <v>3:55</v>
       </c>
       <c r="H170" t="str">
-        <v>Cautious Clay</v>
+        <v>Max McNown</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L170" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Scoreboard</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G171" t="str">
-        <v>3:24</v>
+        <v>2:10</v>
       </c>
       <c r="H171" t="str">
-        <v>Gabriella Rose</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L171" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>High</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:24</v>
       </c>
       <c r="H172" t="str">
-        <v>Nia Smith</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L172" t="str">
-        <v>High - Nia Smith</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Ay Gyal</v>
+        <v>High</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G173" t="str">
-        <v>2:12</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>1Ski OG</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L173" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>always knew</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>always knew - Single</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:25</v>
+        <v>2:12</v>
       </c>
       <c r="H174" t="str">
-        <v>Biscits</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L174" t="str">
-        <v>always knew - Biscits</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cigarette Burns</v>
+        <v>always knew</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:41</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>Corey Kent</v>
+        <v>Biscits</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L175" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Let You Down</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>El Relevo</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G176" t="str">
-        <v>4:14</v>
+        <v>2:41</v>
       </c>
       <c r="H176" t="str">
-        <v>Luis Figueroa</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L176" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Starless</v>
+        <v>Let You Down</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Starless - Single</v>
+        <v>El Relevo</v>
       </c>
       <c r="G177" t="str">
-        <v>4:32</v>
+        <v>4:14</v>
       </c>
       <c r="H177" t="str">
-        <v>A Perfect Circle</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L177" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking For You</v>
+        <v>Starless</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking For You - Single</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:19</v>
+        <v>4:32</v>
       </c>
       <c r="H178" t="str">
-        <v>Gable Price and Friends</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>FOCUSED</v>
+        <v>Looking For You</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-30</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:23</v>
+        <v>3:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Shepherd</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L179" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-30</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:23</v>
+        <v>2:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Shepherd</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L180" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>dream state</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-30</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>dream state - Single</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L181" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>dream state</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-30</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:39</v>
+        <v>4:01</v>
       </c>
       <c r="H182" t="str">
-        <v>Mynolia</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L182" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-30</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Inferno</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>5:25</v>
+        <v>3:39</v>
       </c>
       <c r="H183" t="str">
-        <v>Boards of Canada</v>
+        <v>Mynolia</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L183" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-30</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G184" t="str">
-        <v>2:34</v>
+        <v>5:25</v>
       </c>
       <c r="H184" t="str">
-        <v>Delroy Edwards</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L184" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>FCUK</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-30</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>FCUK - Single</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:22</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>H.LLS</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L185" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Higher</v>
+        <v>FCUK</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-30</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:06</v>
+        <v>2:22</v>
       </c>
       <c r="H186" t="str">
-        <v>Francis of Delirium</v>
+        <v>H.LLS</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L186" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>B.U.N</v>
+        <v>Higher</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-30</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>B.U.N - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G187" t="str">
-        <v>3:43</v>
+        <v>4:06</v>
       </c>
       <c r="H187" t="str">
-        <v>Roll Deep</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L187" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>B.U.N</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-30</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Here Because of Hope</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H188" t="str">
-        <v>Ezra Collective</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L188" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-30</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>UNDRA</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G189" t="str">
-        <v>2:49</v>
+        <v>3:22</v>
       </c>
       <c r="H189" t="str">
-        <v>reggie</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L189" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-30</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>UNDRA</v>
       </c>
       <c r="G190" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H190" t="str">
-        <v>Johnny Huynh</v>
+        <v>reggie</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L190" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Fallen Angel</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-30</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>You Don't Know My Name</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G191" t="str">
-        <v>3:05</v>
+        <v>2:54</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby J</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L191" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Last Encounter</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-30</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G192" t="str">
-        <v>3:04</v>
+        <v>3:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Sofia Camara</v>
+        <v>Baby J</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L192" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>We Fall</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-30</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>We Fall - Single</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:01</v>
+        <v>3:04</v>
       </c>
       <c r="H193" t="str">
-        <v>MOIO</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L193" t="str">
-        <v>We Fall - MOIO</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Don't Know Me</v>
+        <v>We Fall</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-30</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:50</v>
+        <v>4:01</v>
       </c>
       <c r="H194" t="str">
-        <v>Isabel Dumaa</v>
+        <v>MOIO</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L194" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-30</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>House Of Mirrors</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:04</v>
+        <v>3:50</v>
       </c>
       <c r="H195" t="str">
-        <v>All Them Witches</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L195" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Iodine</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-30</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Neverending</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G196" t="str">
-        <v>3:40</v>
+        <v>4:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Monolord</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L196" t="str">
-        <v>Iodine - Monolord</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Iodine</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-30</v>
@@ -7861,68 +7861,106 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>...By the Word...</v>
+        <v>Neverending</v>
       </c>
       <c r="G197" t="str">
-        <v>5:01</v>
+        <v>3:40</v>
       </c>
       <c r="H197" t="str">
-        <v>Trelldom</v>
+        <v>Monolord</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L197" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
+        <v>I Speak Forgotten Voices</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>...By the Word...</v>
+      </c>
+      <c r="G198" t="str">
+        <v>5:01</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Trelldom</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+      </c>
+      <c r="L198" t="str">
+        <v>I Speak Forgotten Voices - Trelldom</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
         <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
-      <c r="D198" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
+      <c r="D199" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
         <v>Rats in the Temple</v>
       </c>
-      <c r="G198" t="str">
+      <c r="G199" t="str">
         <v>4:45</v>
       </c>
-      <c r="H198" t="str">
+      <c r="H199" t="str">
         <v>Flotsam and Jetsam</v>
       </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
         <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
-      <c r="K198" t="str">
+      <c r="K199" t="str">
         <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
-      <c r="L198" t="str">
+      <c r="L199" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי עברון – בא מלמטה</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-30</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%a2%d7%91%d7%a8%d7%95%d7%9f-%d7%91%d7%90-%d7%9e%d7%9c%d7%9e%d7%98%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-30</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"בא מלמטה" של איתי עברון  הוא שיר רוק קברטי-תיאטרלי שמציג דיוקן עצמי חסר מעצורים של אמן צעיר הנאבק בין הצורך להתקבל לבין הדחף להיות נאמן לאש הפנימית שלו. זהו שיר על זהות, מעמד, שאפתנות ועל הסירוב להתנצל על מי שאתה.</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Dua Lipa</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי עברון – בא מלמטה</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-30</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dua Lipa</v>
+        <v>Dagny</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-30</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dagny</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-30</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-30</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Dogpark</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-30</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Dogpark</v>
+        <v>elijah woods</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-30</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>elijah woods</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-30</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Lauren Alaina</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-30</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Lauren Sanderson</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-30</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>NIGHTLY</v>
+        <v>Dasha</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-30</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Dasha</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-30</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Ariana Grande</v>
+        <v>Max McNown</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-30</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Max McNown</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-30</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Bebe Rexha</v>
+        <v>Knox</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-30</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Knox</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-30</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Sofia Camara</v>
+        <v>Alexander James</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-30</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Alexander James</v>
+        <v>almost monday</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-30</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>almost monday</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-30</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Kip Moore</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-30</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Santana</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B22" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-30</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Santana</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B23" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-30</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dua Lipa</v>
+        <v>Charley</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Charley - Liar</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-30</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Charley</v>
+        <v>David Guetta</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-30</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>David Guetta</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B26" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-30</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Jordana Bryant</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B27" t="str">
-        <v>1d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-30</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-30</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-30</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Julia Cole Music</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-30</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>VictorBiliac</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-30</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-30</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Jungle4eva</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B33" t="str">
-        <v>2d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-30</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>DAYTIME TV</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B34" t="str">
-        <v>2w ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-30</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2w ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B35" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-30</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Bruno Mars</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-30</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Keith Urban</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B37" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-30</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Nelly Furtado</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-30</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B39" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-30</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B40" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-30</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Lainey Wilson</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B41" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-30</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Duran Duran</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B42" t="str">
-        <v>9d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-30</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Nico Santos</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-30</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Will Linley</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-30</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Will Linley</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-30</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Kylie Minogue</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B46" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-30</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Billy Raffoul</v>
+        <v>The Offspring</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B47" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-30</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>The Offspring</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B48" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-30</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>David Gilmour</v>
+        <v>Scorpions</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B49" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-30</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Scorpions</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-30</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-30</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>The Warning</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B52" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-30</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>The Warning</v>
+        <v>paris jackson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B53" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-30</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>paris jackson</v>
+        <v>Minelli</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-30</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Minelli</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-30</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Maggie Rose</v>
+        <v>David Guetta</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-30</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>David Guetta</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-30</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Lauv</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-30</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Lauv</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-30</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Icona Pop</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-30</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Will Swinton</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-30</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Dean Lewis</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-30</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-30</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Niall Horan</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-30</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>RUEL</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B65" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-30</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>RUEL</v>
+        <v>TINI</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-30</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>TINI</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B67" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-30</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Charli xcx</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-30</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Dua Lipa</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B69" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-30</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Matilda Mann</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-30</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Ella Langley</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B71" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-30</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Nothing But Thieves</v>
+        <v>kesha</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B72" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-30</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>kesha</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-30</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Holly Humberstone</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B74" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-30</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Foo Fighters</v>
+        <v>The Analogues</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-30</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>The Analogues</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-30</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Rod Stewart</v>
+        <v>Blue October</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-30</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Blue October</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-30</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Far Caspian</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B79" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-30</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Kenia Os</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B80" t="str">
-        <v>10d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-30</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B81" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-30</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B82" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-30</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-30</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B84" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-30</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B85" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-30</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-30</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Evanescence</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-30</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Evanescence</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-30</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B89" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-30</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Armin van Buuren</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-30</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Madison Cunningham</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-30</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Johnny Orlando</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-30</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Carver Jones</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-30</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Jazmin bean</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-30</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Baby Queen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-30</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Switchfoot</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-30</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Grace Potter</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-30</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-30</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>The All-American Rejects</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-30</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Henry Moodie</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-30</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Spacey Jane</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-30</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Megan Moroney</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B102" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-30</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2w ago</v>
+        <v>petal</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H102" t="str">
-        <v>Matt Hansen</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L102" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>hate that i made you love me</v>
+        <v>Come Inside</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-30</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>petal</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G103" t="str">
-        <v>3:17</v>
+        <v>3:13</v>
       </c>
       <c r="H103" t="str">
-        <v>Ariana Grande</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L103" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Come Inside</v>
+        <v>Game Time</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-30</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>Future</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L104" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Game Time</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-30</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:26</v>
+        <v>2:36</v>
       </c>
       <c r="H105" t="str">
-        <v>Future</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L105" t="str">
-        <v>Game Time - Future</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-30</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G106" t="str">
-        <v>2:36</v>
+        <v>3:22</v>
       </c>
       <c r="H106" t="str">
-        <v>Bossman Dlow</v>
+        <v>Young Miko</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L106" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Aquel diciembre</v>
+        <v>Handle</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-30</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>Blue Island</v>
       </c>
       <c r="G107" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H107" t="str">
-        <v>Young Miko</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L107" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Handle</v>
+        <v>The Wave</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-30</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Blue Island</v>
+        <v>Sunshine</v>
       </c>
       <c r="G108" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H108" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Jungle</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L108" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>The Wave</v>
+        <v>STOP</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-30</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sunshine</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:22</v>
+        <v>2:56</v>
       </c>
       <c r="H109" t="str">
-        <v>Jungle</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L109" t="str">
-        <v>The Wave - Jungle</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>STOP</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-30</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G110" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H110" t="str">
-        <v>Bella Kay</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L110" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-30</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Apple Music Sessions</v>
+        <v>The Thread</v>
       </c>
       <c r="G111" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H111" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>WILLOW</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L111" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Talk On The Hill</v>
+        <v>No Fear</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-30</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>The Thread</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G112" t="str">
-        <v>3:27</v>
+        <v>3:38</v>
       </c>
       <c r="H112" t="str">
-        <v>WILLOW</v>
+        <v>Iceage</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L112" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No Fear</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-30</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Big Mama</v>
       </c>
       <c r="G113" t="str">
-        <v>3:38</v>
+        <v>3:11</v>
       </c>
       <c r="H113" t="str">
-        <v>Iceage</v>
+        <v>Latto</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L113" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-30</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Big Mama</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H114" t="str">
-        <v>Latto</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L114" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Sad Girls</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-30</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H115" t="str">
-        <v>Bebe Rexha</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L115" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>Rubio</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G116" t="str">
-        <v>3:35</v>
+        <v>4:42</v>
       </c>
       <c r="H116" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L116" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Rubio</v>
+        <v>Pary</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>La Voz Favorita</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>4:42</v>
+        <v>2:52</v>
       </c>
       <c r="H117" t="str">
-        <v>Jay Wheeler</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L117" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Pary</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Con dolor - EP</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G118" t="str">
-        <v>2:52</v>
+        <v>3:48</v>
       </c>
       <c r="H118" t="str">
-        <v>Grupo Frontera</v>
+        <v>Riley Green</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L118" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Think As You Drunk</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>That's Just Me</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:48</v>
+        <v>3:15</v>
       </c>
       <c r="H119" t="str">
-        <v>Riley Green</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L119" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Play Your Games</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Play Your Games - Single</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:15</v>
+        <v>2:47</v>
       </c>
       <c r="H120" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L120" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:47</v>
+        <v>4:49</v>
       </c>
       <c r="H121" t="str">
-        <v>Tom Morello</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L121" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>minute</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>4:49</v>
+        <v>2:59</v>
       </c>
       <c r="H122" t="str">
-        <v>Blood Orange</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L122" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>minute</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ghosted - EP</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>2:59</v>
+        <v>2:48</v>
       </c>
       <c r="H123" t="str">
-        <v>Saint Harison</v>
+        <v>Labrinth</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L123" t="str">
-        <v>minute - Saint Harison</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>THE LIVING</v>
+        <v>Thug</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:48</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Labrinth</v>
+        <v>G Herbo</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L124" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thug</v>
+        <v>Clap</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Thug - Single</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:25</v>
+        <v>2:04</v>
       </c>
       <c r="H125" t="str">
-        <v>G Herbo</v>
+        <v>Polo G</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L125" t="str">
-        <v>Thug - G Herbo</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Clap</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Clap - Single</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G126" t="str">
-        <v>2:04</v>
+        <v>2:47</v>
       </c>
       <c r="H126" t="str">
-        <v>Polo G</v>
+        <v>YG</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L126" t="str">
-        <v>Clap - Polo G</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>GANG BIZNESS</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G127" t="str">
-        <v>2:47</v>
+        <v>2:50</v>
       </c>
       <c r="H127" t="str">
-        <v>YG</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L127" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G128" t="str">
         <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Jessie Reyez</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L128" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Joshua Tree</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:50</v>
+        <v>3:37</v>
       </c>
       <c r="H129" t="str">
-        <v>Hans Zimmer</v>
+        <v>Santana</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L129" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Mi Gran Amor</v>
+        <v>london</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:37</v>
+        <v>3:23</v>
       </c>
       <c r="H130" t="str">
-        <v>Santana</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L130" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>london</v>
+        <v>Caution</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>stardust - EP</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G131" t="str">
-        <v>3:23</v>
+        <v>2:43</v>
       </c>
       <c r="H131" t="str">
-        <v>Freya Skye</v>
+        <v>NMIXX</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L131" t="str">
-        <v>london - Freya Skye</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Caution</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G132" t="str">
-        <v>2:43</v>
+        <v>3:07</v>
       </c>
       <c r="H132" t="str">
-        <v>NMIXX</v>
+        <v>aespa</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L132" t="str">
-        <v>Caution - NMIXX</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G133" t="str">
-        <v>3:07</v>
+        <v>2:58</v>
       </c>
       <c r="H133" t="str">
-        <v>aespa</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L133" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:58</v>
+        <v>2:42</v>
       </c>
       <c r="H134" t="str">
-        <v>Cody Johnson</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L134" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Cheap Thrills</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G135" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H135" t="str">
-        <v>Gavin Adcock</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L135" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ME VALE V</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>ACOMODO</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G136" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H136" t="str">
-        <v>Tito Double P</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L136" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Bug In The Cake</v>
+        <v>Coil</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G137" t="str">
-        <v>2:48</v>
+        <v>3:54</v>
       </c>
       <c r="H137" t="str">
-        <v>Violet Grohl</v>
+        <v>ear</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L137" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Coil</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Rumspringa</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:54</v>
+        <v>3:30</v>
       </c>
       <c r="H138" t="str">
-        <v>ear</v>
+        <v>Kneecap</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L138" t="str">
-        <v>Coil - ear</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:30</v>
+        <v>3:04</v>
       </c>
       <c r="H139" t="str">
-        <v>Kneecap</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L139" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Out of my Head</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:04</v>
+        <v>3:18</v>
       </c>
       <c r="H140" t="str">
-        <v>Cara Delevingne</v>
+        <v>Perrie</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L140" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Passenger Princess</v>
+        <v>Man of the House</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G141" t="str">
-        <v>3:18</v>
+        <v>2:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Perrie</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L141" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Man of the House</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>SE9</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:35</v>
+        <v>2:37</v>
       </c>
       <c r="H142" t="str">
-        <v>Skye Newman</v>
+        <v>MEEK</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L142" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Beautiful Freeks</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:37</v>
+        <v>4:34</v>
       </c>
       <c r="H143" t="str">
-        <v>MEEK</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L143" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>4:34</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>ILLENIUM</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L144" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>1:45</v>
       </c>
       <c r="H145" t="str">
-        <v>Lily Allen</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L145" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ABOVE IT</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:45</v>
+        <v>4:15</v>
       </c>
       <c r="H146" t="str">
-        <v>Andy Mineo</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L146" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:15</v>
+        <v>3:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Forrest Frank</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L147" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Is It Over Now?</v>
+        <v>12 Steps</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:39</v>
+        <v>3:11</v>
       </c>
       <c r="H148" t="str">
-        <v>Elderbrook</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L148" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>12 Steps</v>
+        <v>Over And Over</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>12 Steps - Single</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G149" t="str">
-        <v>3:11</v>
+        <v>4:38</v>
       </c>
       <c r="H149" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L149" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Over And Over</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>It's A Dying Art</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G150" t="str">
-        <v>4:38</v>
+        <v>2:22</v>
       </c>
       <c r="H150" t="str">
-        <v>Little Big Town</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L150" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>AMAPOLA</v>
+        <v>Mad About It</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ricky y Mau</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:22</v>
+        <v>2:37</v>
       </c>
       <c r="H151" t="str">
-        <v>Mau y Ricky</v>
+        <v>Dasha</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L151" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mad About It</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mad About It - Single</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:37</v>
+        <v>2:59</v>
       </c>
       <c r="H152" t="str">
-        <v>Dasha</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L152" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Love’s a Gun</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:59</v>
+        <v>2:48</v>
       </c>
       <c r="H153" t="str">
-        <v>Daniel Seavey</v>
+        <v>Knox</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L153" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Long Story Short</v>
+        <v>blue jeans</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Long Story Short - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:48</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Knox</v>
+        <v>Nightly</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L154" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>blue jeans</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>blue jeans - Single</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>3:13</v>
       </c>
       <c r="H155" t="str">
-        <v>Nightly</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L155" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Que Gacho</v>
+        <v>same God</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Que Gacho - Single</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G156" t="str">
-        <v>3:13</v>
+        <v>3:34</v>
       </c>
       <c r="H156" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L156" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>same God</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>IDCASH</v>
       </c>
       <c r="G157" t="str">
-        <v>3:34</v>
+        <v>2:12</v>
       </c>
       <c r="H157" t="str">
-        <v>Alana Springsteen</v>
+        <v>IDK</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L157" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>emotional swaggage</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>IDCASH</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:12</v>
+        <v>3:36</v>
       </c>
       <c r="H158" t="str">
-        <v>IDK</v>
+        <v>070 Shake</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L158" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Baby Driver</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Baby Driver - Single</v>
+        <v>REBECCA</v>
       </c>
       <c r="G159" t="str">
-        <v>3:36</v>
+        <v>2:55</v>
       </c>
       <c r="H159" t="str">
-        <v>070 Shake</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L159" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>More! More! More!</v>
+        <v>Young Again</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>REBECCA</v>
+        <v>EI8HT</v>
       </c>
       <c r="G160" t="str">
-        <v>2:55</v>
+        <v>3:36</v>
       </c>
       <c r="H160" t="str">
-        <v>Becky Hill</v>
+        <v>Shinedown</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L160" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Young Again</v>
+        <v>skinny dip</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>EI8HT</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:36</v>
+        <v>3:12</v>
       </c>
       <c r="H161" t="str">
-        <v>Shinedown</v>
+        <v>almost monday</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L161" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>skinny dip</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>skinny dip - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G162" t="str">
-        <v>3:12</v>
+        <v>4:14</v>
       </c>
       <c r="H162" t="str">
-        <v>almost monday</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L162" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>Better Off</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>girls like girls the album</v>
+        <v>Stages</v>
       </c>
       <c r="G163" t="str">
-        <v>4:14</v>
+        <v>3:16</v>
       </c>
       <c r="H163" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L163" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Better Off</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Stages</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:16</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Lauren Alaina</v>
+        <v>Monaleo</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L164" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G165" t="str">
-        <v>2:48</v>
+        <v>3:30</v>
       </c>
       <c r="H165" t="str">
-        <v>Monaleo</v>
+        <v>R3HAB</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L165" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Lost in translation...</v>
+        <v>Call Security</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Dream inside a dream…</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G166" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H166" t="str">
-        <v>R3HAB</v>
+        <v>Chxrry</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L166" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Call Security</v>
+        <v>chaotic</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G167" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H167" t="str">
-        <v>Chxrry</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L167" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>chaotic</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>scars to prove it</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>4:17</v>
       </c>
       <c r="H168" t="str">
-        <v>Hailey Picardi</v>
+        <v>Love Spells</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L168" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Keep It To Yourself</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:17</v>
+        <v>3:55</v>
       </c>
       <c r="H169" t="str">
-        <v>Love Spells</v>
+        <v>Max McNown</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L169" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Something to Someone</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Something to Someone - Single</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G170" t="str">
-        <v>3:55</v>
+        <v>2:10</v>
       </c>
       <c r="H170" t="str">
-        <v>Max McNown</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L170" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Hours: High Noon</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G171" t="str">
-        <v>2:10</v>
+        <v>3:24</v>
       </c>
       <c r="H171" t="str">
-        <v>Cautious Clay</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L171" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Scoreboard</v>
+        <v>High</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/high/6773775211</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>Payback Is A Dog (EP)</v>
       </c>
       <c r="G172" t="str">
-        <v>3:24</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>Gabriella Rose</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/high/6773775203</v>
       </c>
       <c r="L172" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>High - Nia Smith</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>High</v>
+        <v>Ay Gyal</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>Ay Gyal - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>2:12</v>
       </c>
       <c r="H173" t="str">
-        <v>Nia Smith</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
       </c>
       <c r="L173" t="str">
-        <v>High - Nia Smith</v>
+        <v>Ay Gyal - 1Ski OG</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ay Gyal</v>
+        <v>always knew</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>always knew - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:12</v>
+        <v>3:25</v>
       </c>
       <c r="H174" t="str">
-        <v>1Ski OG</v>
+        <v>Biscits</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
       </c>
       <c r="L174" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>always knew - Biscits</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>always knew</v>
+        <v>Cigarette Burns</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>always knew - Single</v>
+        <v>Heartland Rock and Roll</v>
       </c>
       <c r="G175" t="str">
-        <v>3:25</v>
+        <v>2:41</v>
       </c>
       <c r="H175" t="str">
-        <v>Biscits</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
       </c>
       <c r="L175" t="str">
-        <v>always knew - Biscits</v>
+        <v>Cigarette Burns - Corey Kent</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Cigarette Burns</v>
+        <v>Let You Down</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>El Relevo</v>
       </c>
       <c r="G176" t="str">
-        <v>2:41</v>
+        <v>4:14</v>
       </c>
       <c r="H176" t="str">
-        <v>Corey Kent</v>
+        <v>Luis Figueroa</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
       </c>
       <c r="L176" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>Let You Down - Luis Figueroa</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Let You Down</v>
+        <v>Starless</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/starless/6770568779</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>El Relevo</v>
+        <v>Starless - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:14</v>
+        <v>4:32</v>
       </c>
       <c r="H177" t="str">
-        <v>Luis Figueroa</v>
+        <v>A Perfect Circle</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/starless/6770568776</v>
       </c>
       <c r="L177" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Starless - A Perfect Circle</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Starless</v>
+        <v>Looking For You</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Starless - Single</v>
+        <v>Looking For You - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:32</v>
+        <v>3:19</v>
       </c>
       <c r="H178" t="str">
-        <v>A Perfect Circle</v>
+        <v>Gable Price and Friends</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
       </c>
       <c r="L178" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Looking For You - Gable Price and Friends</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Looking For You</v>
+        <v>FOCUSED</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/focused/1887909237</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-30</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Looking For You - Single</v>
+        <v>FOCUSED - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:19</v>
+        <v>2:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Shepherd</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/focused/1887909236</v>
       </c>
       <c r="L179" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>FOCUSED - Shepherd</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>FOCUSED</v>
+        <v>Tú Ni En Cuenta</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/focused/1887909237</v>
+        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-30</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>FOCUSED - Single</v>
+        <v>Tú Ni En Cuenta - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:23</v>
+        <v>3:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Shepherd</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/shepherd/1192803216</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/focused/1887909236</v>
+        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
       </c>
       <c r="L180" t="str">
-        <v>FOCUSED - Shepherd</v>
+        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Tú Ni En Cuenta</v>
+        <v>dream state</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/tu-ni-en-cuenta/6767701804</v>
+        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-30</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Tú Ni En Cuenta - Single</v>
+        <v>dream state - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H181" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Martin Luke Brown</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/tu-ni-en-cuenta/6767701803</v>
+        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
       </c>
       <c r="L181" t="str">
-        <v>Tú Ni En Cuenta - Banda MS de Sergio Lizárraga</v>
+        <v>dream state - Martin Luke Brown</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>dream state</v>
+        <v>Needle (feat. Spencer Cullum)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/dream-state/6765596009</v>
+        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-30</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>dream state - Single</v>
+        <v>Needle (feat. Spencer Cullum) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:01</v>
+        <v>3:39</v>
       </c>
       <c r="H182" t="str">
-        <v>Martin Luke Brown</v>
+        <v>Mynolia</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/martin-luke-brown/883292185</v>
+        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/dream-state/1896004790</v>
+        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
       </c>
       <c r="L182" t="str">
-        <v>dream state - Martin Luke Brown</v>
+        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Needle (feat. Spencer Cullum)</v>
+        <v>You Retreat In Time And Space</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/needle-feat-spencer-cullum/6767618217</v>
+        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-30</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Needle (feat. Spencer Cullum) - Single</v>
+        <v>Inferno</v>
       </c>
       <c r="G183" t="str">
-        <v>3:39</v>
+        <v>5:25</v>
       </c>
       <c r="H183" t="str">
-        <v>Mynolia</v>
+        <v>Boards of Canada</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mynolia/1444347510</v>
+        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/needle-feat-spencer-cullum/6767618203</v>
+        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
       </c>
       <c r="L183" t="str">
-        <v>Needle (feat. Spencer Cullum) - Mynolia</v>
+        <v>You Retreat In Time And Space - Boards of Canada</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>You Retreat In Time And Space</v>
+        <v>It's Happening (To Me)</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/you-retreat-in-time-and-space/1890015660</v>
+        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-30</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Inferno</v>
+        <v>It's Happening (To Me) - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>5:25</v>
+        <v>2:34</v>
       </c>
       <c r="H184" t="str">
-        <v>Boards of Canada</v>
+        <v>Delroy Edwards</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/boards-of-canada/2989314</v>
+        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/you-retreat-in-time-and-space/1890015523</v>
+        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
       </c>
       <c r="L184" t="str">
-        <v>You Retreat In Time And Space - Boards of Canada</v>
+        <v>It's Happening (To Me) - Delroy Edwards</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>It's Happening (To Me)</v>
+        <v>FCUK</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/its-happening-to-me/6764723461</v>
+        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-30</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>It's Happening (To Me) - Single</v>
+        <v>FCUK - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:34</v>
+        <v>2:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Delroy Edwards</v>
+        <v>H.LLS</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/delroy-edwards/591790909</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/its-happening-to-me/1895893472</v>
+        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
       </c>
       <c r="L185" t="str">
-        <v>It's Happening (To Me) - Delroy Edwards</v>
+        <v>FCUK - H.LLS</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>FCUK</v>
+        <v>Higher</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/fcuk/6769623577</v>
+        <v>https://music.apple.com/us/song/higher/1880124200</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-30</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>FCUK - Single</v>
+        <v>Run, Run Pure Beauty</v>
       </c>
       <c r="G186" t="str">
-        <v>2:22</v>
+        <v>4:06</v>
       </c>
       <c r="H186" t="str">
-        <v>H.LLS</v>
+        <v>Francis of Delirium</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/fcuk/6769623566</v>
+        <v>https://music.apple.com/us/album/higher/1880123731</v>
       </c>
       <c r="L186" t="str">
-        <v>FCUK - H.LLS</v>
+        <v>Higher - Francis of Delirium</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Higher</v>
+        <v>B.U.N</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/higher/1880124200</v>
+        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-30</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Run, Run Pure Beauty</v>
+        <v>B.U.N - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:06</v>
+        <v>3:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Francis of Delirium</v>
+        <v>Roll Deep</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/francis-of-delirium/1485902996</v>
+        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/higher/1880123731</v>
+        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
       </c>
       <c r="L187" t="str">
-        <v>Higher - Francis of Delirium</v>
+        <v>B.U.N - Roll Deep</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>B.U.N</v>
+        <v>Only Love (feat. Pa Salieu)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/b-u-n/6763272338</v>
+        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-30</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>B.U.N - Single</v>
+        <v>Here Because of Hope</v>
       </c>
       <c r="G188" t="str">
-        <v>3:43</v>
+        <v>3:22</v>
       </c>
       <c r="H188" t="str">
-        <v>Roll Deep</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/roll-deep/3083873</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/b-u-n/1895242397</v>
+        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
       </c>
       <c r="L188" t="str">
-        <v>B.U.N - Roll Deep</v>
+        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Only Love (feat. Pa Salieu)</v>
+        <v>Beautiful Things 1st scene/audition</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/only-love-feat-pa-salieu/6767014290</v>
+        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-30</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Here Because of Hope</v>
+        <v>UNDRA</v>
       </c>
       <c r="G189" t="str">
-        <v>3:22</v>
+        <v>2:49</v>
       </c>
       <c r="H189" t="str">
-        <v>Ezra Collective</v>
+        <v>reggie</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/only-love-feat-pa-salieu/6767014278</v>
+        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
       </c>
       <c r="L189" t="str">
-        <v>Only Love (feat. Pa Salieu) - Ezra Collective</v>
+        <v>Beautiful Things 1st scene/audition - reggie</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Beautiful Things 1st scene/audition</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/beautiful-things-1st-scene-audition/6771942631</v>
+        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-30</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>UNDRA</v>
+        <v>HEAVEN'S ON FIRE</v>
       </c>
       <c r="G190" t="str">
-        <v>2:49</v>
+        <v>2:54</v>
       </c>
       <c r="H190" t="str">
-        <v>reggie</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/reggie/1526587068</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/beautiful-things-1st-scene-audition/6771942630</v>
+        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
       </c>
       <c r="L190" t="str">
-        <v>Beautiful Things 1st scene/audition - reggie</v>
+        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>Fallen Angel</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/heavens-on-fire/6771110730</v>
+        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-30</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>HEAVEN'S ON FIRE</v>
+        <v>You Don't Know My Name</v>
       </c>
       <c r="G191" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Johnny Huynh</v>
+        <v>Baby J</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/heavens-on-fire/6771110729</v>
+        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
       </c>
       <c r="L191" t="str">
-        <v>HEAVEN'S ON FIRE - Johnny Huynh</v>
+        <v>Fallen Angel - Baby J</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Fallen Angel</v>
+        <v>The Last Encounter</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/fallen-angel/6771161222</v>
+        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-30</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>You Don't Know My Name</v>
+        <v>The Last Encounter - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Baby J</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/fallen-angel/6771161180</v>
+        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
       </c>
       <c r="L192" t="str">
-        <v>Fallen Angel - Baby J</v>
+        <v>The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Last Encounter</v>
+        <v>We Fall</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-last-encounter/6767395134</v>
+        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-30</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Last Encounter - Single</v>
+        <v>We Fall - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:04</v>
+        <v>4:01</v>
       </c>
       <c r="H193" t="str">
-        <v>Sofia Camara</v>
+        <v>MOIO</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/sofia-camara/1506432156</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-last-encounter/6767395133</v>
+        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
       </c>
       <c r="L193" t="str">
-        <v>The Last Encounter - Sofia Camara</v>
+        <v>We Fall - MOIO</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>We Fall</v>
+        <v>You Don't Know Me</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/we-fall/6769218917</v>
+        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-30</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>We Fall - Single</v>
+        <v>You Don’t Know Me - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:01</v>
+        <v>3:50</v>
       </c>
       <c r="H194" t="str">
-        <v>MOIO</v>
+        <v>Isabel Dumaa</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/we-fall/6769218915</v>
+        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
       </c>
       <c r="L194" t="str">
-        <v>We Fall - MOIO</v>
+        <v>You Don't Know Me - Isabel Dumaa</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>You Don't Know Me</v>
+        <v>Hold Up, Say What?</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/you-dont-know-me/6769214417</v>
+        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-30</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>You Don’t Know Me - Single</v>
+        <v>House Of Mirrors</v>
       </c>
       <c r="G195" t="str">
-        <v>3:50</v>
+        <v>4:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Isabel Dumaa</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/isabel-dumaa/1631481156</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/you-dont-know-me/6769214410</v>
+        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
       </c>
       <c r="L195" t="str">
-        <v>You Don't Know Me - Isabel Dumaa</v>
+        <v>Hold Up, Say What? - All Them Witches</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Hold Up, Say What?</v>
+        <v>Iodine</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/hold-up-say-what/1879853511</v>
+        <v>https://music.apple.com/us/song/iodine/1871211805</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-30</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>House Of Mirrors</v>
+        <v>Neverending</v>
       </c>
       <c r="G196" t="str">
-        <v>4:04</v>
+        <v>3:40</v>
       </c>
       <c r="H196" t="str">
-        <v>All Them Witches</v>
+        <v>Monolord</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/hold-up-say-what/1879853502</v>
+        <v>https://music.apple.com/us/album/iodine/1871211801</v>
       </c>
       <c r="L196" t="str">
-        <v>Hold Up, Say What? - All Them Witches</v>
+        <v>Iodine - Monolord</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Iodine</v>
+        <v>I Speak Forgotten Voices</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/iodine/1871211805</v>
+        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-30</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Neverending</v>
+        <v>...By the Word...</v>
       </c>
       <c r="G197" t="str">
-        <v>3:40</v>
+        <v>5:01</v>
       </c>
       <c r="H197" t="str">
-        <v>Monolord</v>
+        <v>Trelldom</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/iodine/1871211801</v>
+        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
       </c>
       <c r="L197" t="str">
-        <v>Iodine - Monolord</v>
+        <v>I Speak Forgotten Voices - Trelldom</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>I Speak Forgotten Voices</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/i-speak-forgotten-voices/1878083625</v>
+        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-30</v>
@@ -7899,68 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>...By the Word...</v>
+        <v>Rats in the Temple</v>
       </c>
       <c r="G198" t="str">
-        <v>5:01</v>
+        <v>4:45</v>
       </c>
       <c r="H198" t="str">
-        <v>Trelldom</v>
+        <v>Flotsam and Jetsam</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/trelldom/256586618</v>
+        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/i-speak-forgotten-voices/1878083622</v>
+        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
       </c>
       <c r="L198" t="str">
-        <v>I Speak Forgotten Voices - Trelldom</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/rats-in-the-temple/6764627559</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Rats in the Temple</v>
-      </c>
-      <c r="G199" t="str">
-        <v>4:45</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Flotsam and Jetsam</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/flotsam-and-jetsam/162270</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/rats-in-the-temple/1895855647</v>
-      </c>
-      <c r="L199" t="str">
         <v>Rats in the Temple - Flotsam and Jetsam</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -1351,7 +1351,7 @@
         <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>

--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>David Guetta</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,7 +1305,7 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="25">
@@ -1503,7 +1503,7 @@
         <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>

--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Charley - Liar</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B33" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/global/2026-05-week05/titles.xlsx
+++ b/data/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>גל חייק - מכתב פרידה</v>
       </c>
       <c r="B2" t="str">
-        <v>1d ago</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411119&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-30</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1d ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Dua Lipa</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>גל חייק - מכתב פרידה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>בן-אל - פתאום נעלמת</v>
       </c>
       <c r="B3" t="str">
-        <v>1d ago</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411117&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-30</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1d ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dagny</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>בן-אל - פתאום נעלמת</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>אמיתי צדוק - כיוון אחד</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411116&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-30</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>אמיתי צדוק - כיוון אחד</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>אלחנן אלחדד &amp; קובי ברומר - אנעים זמירות</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411115&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-30</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>אלחנן אלחדד &amp; קובי ברומר - אנעים זמירות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>אלחי מידני - שכחתי לחייך</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411114&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-30</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Dogpark</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>אלחי מידני - שכחתי לחייך</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
+        <v>איתי כהן - אל תדאגי לי</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411113&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-30</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>elijah woods</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
+        <v>איתי כהן - אל תדאגי לי</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio)</v>
+        <v>Kaan Ates - Sen Ve Ben (Bedal)</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411112&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-30</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Lauren Alaina</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
+        <v>Kaan Ates - Sen Ve Ben (Bedal)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
+        <v>Dua Lipa - Physical (Live From Mexico)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
+        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-30</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
+        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video)</v>
+        <v>Dagny - Rain (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
+        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-30</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>NIGHTLY</v>
+        <v>Dagny</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
+        <v>Dagny - Rain (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dasha - Mad About It (Official Visualizer)</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
+        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-30</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Dasha</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
+        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
+        <v>Jonas Blue - Girl (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
+        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-30</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ariana Grande</v>
+        <v>Defected Records and Jonas Blue</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
+        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Max McNown - Something To Someone (Performance Video)</v>
+        <v>Dogpark - Don't Lie (Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
+        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-30</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Max McNown</v>
+        <v>Dogpark</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
+        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions)</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
+        <v>https://www.youtube.com/watch?v=q5kN7eH6rgo</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-30</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Bebe Rexha</v>
+        <v>elijah woods</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
+        <v>elijah woods - L-O-V-E (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Knox - Long Story Short (Official Video)</v>
+        <v>Lauren Alaina - Better Off (Official Audio)</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
+        <v>https://www.youtube.com/watch?v=Vj-ong3XNHM</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-30</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Knox</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Knox - Long Story Short (Official Video) - Knox</v>
+        <v>Lauren Alaina - Better Off (Official Audio) - Lauren Alaina</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Sofia Camara - The Last Encounter</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
+        <v>https://www.youtube.com/watch?v=u7Et_hbMZUA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-30</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Sofia Camara</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
+        <v>Lauren Sanderson - ARE YOU REALLY HERE? (Lyric Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James</v>
+        <v>Nightly – blue jeans (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
+        <v>https://www.youtube.com/watch?v=LnA3xkXUwaM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-30</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Alexander James</v>
+        <v>NIGHTLY</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
+        <v>Nightly – blue jeans (Official Lyric Video) - NIGHTLY</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>almost monday - skinny dip (official video)</v>
+        <v>Dasha - Mad About It (Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
+        <v>https://www.youtube.com/watch?v=Ae1gf_7p3H8</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-30</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>almost monday</v>
+        <v>Dasha</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>almost monday - skinny dip (official video) - almost monday</v>
+        <v>Dasha - Mad About It (Official Visualizer) - Dasha</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kip Moore - The Darkness (Official)</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video)</v>
       </c>
       <c r="B19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
+        <v>https://www.youtube.com/watch?v=v1t4MTqdfyI</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-30</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Kip Moore</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
+        <v>Ariana Grande - hate that i made you love me (official lyric video) - Ariana Grande</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video)</v>
+        <v>Max McNown - Something To Someone (Performance Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
+        <v>https://www.youtube.com/watch?v=4Ki4ejT86YM</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-30</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Max McNown</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Max McNown - Something To Someone (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual)</v>
       </c>
       <c r="B21" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
+        <v>https://www.youtube.com/watch?v=P8UqZ5IF-QE</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-30</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Santana</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
+        <v>Bebe Rexha &amp; David Guetta - Sad Girls (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico)</v>
+        <v>Knox - Long Story Short (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
+        <v>https://www.youtube.com/watch?v=5OGY6hCELfg</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-30</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dua Lipa</v>
+        <v>Knox</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
+        <v>Knox - Long Story Short (Official Video) - Knox</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Charley - Liar</v>
+        <v>Sofia Camara - The Last Encounter</v>
       </c>
       <c r="B23" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
+        <v>https://www.youtube.com/watch?v=E9kN4HLGG1c</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-30</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Charley</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Charley - Liar - Charley</v>
+        <v>Sofia Camara - The Last Encounter - Sofia Camara</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
+        <v>Official Music Video: "Flowers" -- Alexander James</v>
       </c>
       <c r="B24" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
+        <v>https://www.youtube.com/watch?v=aZ4WP0P92tM</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-30</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Alexander James</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
+        <v>Official Music Video: "Flowers" -- Alexander James - Alexander James</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
+        <v>almost monday - skinny dip (official video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
+        <v>https://www.youtube.com/watch?v=hOxZDoaIzKQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-30</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Jordana Bryant</v>
+        <v>almost monday</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
+        <v>almost monday - skinny dip (official video) - almost monday</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lewis Capaldi - Stay Love</v>
+        <v>Kip Moore - The Darkness (Official)</v>
       </c>
       <c r="B26" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
+        <v>https://www.youtube.com/watch?v=lTqqixCt5Mk</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-30</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
+        <v>Kip Moore - The Darkness (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
+        <v>Paul McCartney - Come Inside (Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
+        <v>https://www.youtube.com/watch?v=C8Zw_Cbm2V0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-30</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
+        <v>Paul McCartney - Come Inside (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Julia Cole - Love You to Death (Official Video)</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
+        <v>https://www.youtube.com/watch?v=btdBd_Yee8E</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-30</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Julia Cole Music</v>
+        <v>Santana</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
+        <v>Santana, Becky G - Mi Gran Amor (Official Lyric Video) - Santana</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
+        <v>Dua Lipa - Training Season (Live From Mexico)</v>
       </c>
       <c r="B29" t="str">
-        <v>3d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
+        <v>https://www.youtube.com/watch?v=Va8Udsvqigs</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-30</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>VictorBiliac</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
+        <v>Dua Lipa - Training Season (Live From Mexico) - Dua Lipa</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
+        <v>Charley - Liar</v>
       </c>
       <c r="B30" t="str">
-        <v>3d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
+        <v>https://www.youtube.com/watch?v=3Erfj2Eecgw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-30</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Lolo Zouaï and disiz</v>
+        <v>Charley</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
+        <v>Charley - Liar - Charley</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jungle - The Wave (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer]</v>
       </c>
       <c r="B31" t="str">
-        <v>3d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
+        <v>https://www.youtube.com/watch?v=em5ryETDkAo</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-30</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Jungle4eva</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (ft Gabito Ballesteros) [Visualizer] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Daytime TV – Sun (Official Music Video)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
+        <v>https://www.youtube.com/watch?v=AmwNx9qlOpA</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-30</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>DAYTIME TV</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Audio) - Jordana Bryant</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
+        <v>Lewis Capaldi - Stay Love</v>
       </c>
       <c r="B33" t="str">
-        <v>2w ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
+        <v>https://www.youtube.com/watch?v=9Pud3BqPpq0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-30</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2w ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
+        <v>Lewis Capaldi - Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B34" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-30</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Bruno Mars</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-30</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Keith Urban</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B36" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-30</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Nelly Furtado</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-30</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-30</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-30</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Lainey Wilson</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B40" t="str">
-        <v>7d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-30</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Duran Duran</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B41" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-30</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Nico Santos</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B42" t="str">
-        <v>7d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-30</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-30</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Will Linley</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B44" t="str">
-        <v>8d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-30</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Kylie Minogue</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-30</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B46" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-30</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>The Offspring</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B47" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-30</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>David Gilmour</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B48" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-30</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Scorpions</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B49" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-30</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-30</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Will Linley</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-30</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>The Warning</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-30</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>paris jackson</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-30</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Minelli</v>
+        <v>The Offspring</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B54" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-30</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Maggie Rose</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-30</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>David Guetta</v>
+        <v>Scorpions</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-30</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-30</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Lauv</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-30</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Icona Pop</v>
+        <v>The Warning</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-30</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Will Swinton</v>
+        <v>paris jackson</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B60" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-30</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Dean Lewis</v>
+        <v>Minelli</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-30</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-30</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Niall Horan</v>
+        <v>David Guetta</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-30</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-30</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>RUEL</v>
+        <v>Lauv</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-30</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>TINI</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-30</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Charli xcx</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-30</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Dua Lipa</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B68" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-30</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Matilda Mann</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-30</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Ella Langley</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-30</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-30</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>kesha</v>
+        <v>RUEL</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B72" t="str">
-        <v>10d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-30</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Holly Humberstone</v>
+        <v>TINI</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>10d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-30</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Foo Fighters</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B74" t="str">
-        <v>10d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-30</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Analogues</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>10d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-30</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Rod Stewart</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B76" t="str">
-        <v>10d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-30</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Blue October</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-30</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Far Caspian</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-30</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Kenia Os</v>
+        <v>kesha</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B79" t="str">
-        <v>11d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-30</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-30</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B81" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-30</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Analogues</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B82" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-30</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-30</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Blue October</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-30</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B85" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-30</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-30</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Evanescence</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-30</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-30</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Armin van Buuren</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-30</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Madison Cunningham</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-30</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Johnny Orlando</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-30</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Carver Jones</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-30</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Jazmin bean</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-30</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Baby Queen</v>
+        <v>Evanescence</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-30</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Switchfoot</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-30</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Grace Potter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-30</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-30</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The All-American Rejects</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-30</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Henry Moodie</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-30</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Spacey Jane</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-30</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Megan Moroney</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-30</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Matt Hansen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>hate that i made you love me</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-30</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>petal</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Ariana Grande</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>hate that i made you love me - Ariana Grande</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Come Inside</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-30</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Paul McCartney</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Come Inside - Paul McCartney</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Game Time</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/game-time/6771157200</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-30</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Game Time (FIFA World Cup 2026™) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:26</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Future</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/future/128050210</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/game-time/6771157186</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Game Time - Future</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Motion Party (Remix)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-30</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Motion Party (Remix) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:36</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Bossman Dlow</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Motion Party (Remix) - Bossman Dlow</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Aquel diciembre</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-30</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Do Not Disturb: Late Checkout</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Young Miko</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Aquel diciembre - Young Miko</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Handle</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/handle/6771922623</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-30</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Blue Island</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:06</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/handle/6771922622</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Handle - Ravyn Lenae</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>The Wave</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-30</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Sunshine</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Jungle</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>STOP</v>
+        <v>hate that i made you love me</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/hate-that-i-made-you-love-me/6763656876</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-30</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>petal</v>
       </c>
       <c r="G109" t="str">
-        <v>2:56</v>
+        <v>3:17</v>
       </c>
       <c r="H109" t="str">
-        <v>Bella Kay</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/hate-that-i-made-you-love-me/1895420989</v>
       </c>
       <c r="L109" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>hate that i made you love me - Ariana Grande</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Here (Apple Music Sessions)</v>
+        <v>Come Inside</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
+        <v>https://music.apple.com/us/song/come-inside/1887403093</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-30</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Apple Music Sessions</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G110" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H110" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
+        <v>https://music.apple.com/us/album/come-inside/1887402919</v>
       </c>
       <c r="L110" t="str">
-        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
+        <v>Come Inside - Paul McCartney</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Talk On The Hill</v>
+        <v>Game Time</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
+        <v>https://music.apple.com/us/song/game-time/6771157200</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-30</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>The Thread</v>
+        <v>Game Time (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:27</v>
+        <v>3:26</v>
       </c>
       <c r="H111" t="str">
-        <v>WILLOW</v>
+        <v>Future</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/future/128050210</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
+        <v>https://music.apple.com/us/album/game-time/6771157186</v>
       </c>
       <c r="L111" t="str">
-        <v>Talk On The Hill - WILLOW</v>
+        <v>Game Time - Future</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No Fear</v>
+        <v>Motion Party (Remix)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
+        <v>https://music.apple.com/us/song/motion-party-remix/6773413965</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-30</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Motion Party (Remix) - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:38</v>
+        <v>2:36</v>
       </c>
       <c r="H112" t="str">
-        <v>Iceage</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
+        <v>https://music.apple.com/us/album/motion-party-remix/6773413953</v>
       </c>
       <c r="L112" t="str">
-        <v>No Fear - Iceage</v>
+        <v>Motion Party (Remix) - Bossman Dlow</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Hostage (feat. 21 Savage)</v>
+        <v>Aquel diciembre</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
+        <v>https://music.apple.com/us/song/aquel-diciembre/6769580010</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-30</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Big Mama</v>
+        <v>Do Not Disturb: Late Checkout</v>
       </c>
       <c r="G113" t="str">
-        <v>3:11</v>
+        <v>3:22</v>
       </c>
       <c r="H113" t="str">
-        <v>Latto</v>
+        <v>Young Miko</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
+        <v>https://music.apple.com/us/album/aquel-diciembre/6769579992</v>
       </c>
       <c r="L113" t="str">
-        <v>Hostage (feat. 21 Savage) - Latto</v>
+        <v>Aquel diciembre - Young Miko</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sad Girls</v>
+        <v>Handle</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-30</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Sad Girls - Single</v>
+        <v>Blue Island</v>
       </c>
       <c r="G114" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H114" t="str">
-        <v>Bebe Rexha</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L114" t="str">
-        <v>Sad Girls - Bebe Rexha</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
+        <v>The Wave</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-30</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G115" t="str">
-        <v>3:35</v>
+        <v>3:22</v>
       </c>
       <c r="H115" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Jungle</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L115" t="str">
-        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Rubio</v>
+        <v>STOP</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/rubio/6770655339</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-30</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>La Voz Favorita</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:42</v>
+        <v>2:56</v>
       </c>
       <c r="H116" t="str">
-        <v>Jay Wheeler</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/rubio/6770654729</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L116" t="str">
-        <v>Rubio - Jay Wheeler</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Pary</v>
+        <v>Here (Apple Music Sessions)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/pary/6767367748</v>
+        <v>https://music.apple.com/us/song/here-apple-music-sessions/1878235516</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-30</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Con dolor - EP</v>
+        <v>Apple Music Sessions</v>
       </c>
       <c r="G117" t="str">
-        <v>2:52</v>
+        <v>3:08</v>
       </c>
       <c r="H117" t="str">
-        <v>Grupo Frontera</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/pary/6767367501</v>
+        <v>https://music.apple.com/us/album/here-apple-music-sessions/1878235330</v>
       </c>
       <c r="L117" t="str">
-        <v>Pary - Grupo Frontera</v>
+        <v>Here (Apple Music Sessions) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Think As You Drunk</v>
+        <v>Talk On The Hill</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
+        <v>https://music.apple.com/us/song/talk-on-the-hill/6769524458</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-30</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>That's Just Me</v>
+        <v>The Thread</v>
       </c>
       <c r="G118" t="str">
-        <v>3:48</v>
+        <v>3:27</v>
       </c>
       <c r="H118" t="str">
-        <v>Riley Green</v>
+        <v>WILLOW</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
+        <v>https://music.apple.com/us/album/talk-on-the-hill/6769524450</v>
       </c>
       <c r="L118" t="str">
-        <v>Think As You Drunk - Riley Green</v>
+        <v>Talk On The Hill - WILLOW</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Play Your Games</v>
+        <v>No Fear</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
+        <v>https://music.apple.com/us/song/no-fear/1880484493</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-30</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Play Your Games - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G119" t="str">
-        <v>3:15</v>
+        <v>3:38</v>
       </c>
       <c r="H119" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Iceage</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
+        <v>https://music.apple.com/us/album/no-fear/1880484160</v>
       </c>
       <c r="L119" t="str">
-        <v>Play Your Games - Greta Van Fleet</v>
+        <v>No Fear - Iceage</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
+        <v>Hostage (feat. 21 Savage)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
+        <v>https://music.apple.com/us/song/hostage-feat-21-savage/6774372288</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-30</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G120" t="str">
-        <v>2:47</v>
+        <v>3:11</v>
       </c>
       <c r="H120" t="str">
-        <v>Tom Morello</v>
+        <v>Latto</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
+        <v>https://music.apple.com/us/album/hostage-feat-21-savage/6774372200</v>
       </c>
       <c r="L120" t="str">
-        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
+        <v>Hostage (feat. 21 Savage) - Latto</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Essex_Honey.mp3</v>
+        <v>Sad Girls</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
+        <v>https://music.apple.com/us/song/sad-girls/6768814374</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-30</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Essex_Honey.mp3 - Single</v>
+        <v>Sad Girls - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:49</v>
+        <v>2:48</v>
       </c>
       <c r="H121" t="str">
-        <v>Blood Orange</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
+        <v>https://music.apple.com/us/album/sad-girls/6768814373</v>
       </c>
       <c r="L121" t="str">
-        <v>Essex_Honey.mp3 - Blood Orange</v>
+        <v>Sad Girls - Bebe Rexha</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>minute</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/minute/1875303122</v>
+        <v>https://music.apple.com/us/song/salvame-hoy-feat-gabito-ballesteros/6765697019</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-30</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ghosted - EP</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H122" t="str">
-        <v>Saint Harison</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/minute/1875302904</v>
+        <v>https://music.apple.com/us/album/salvame-hoy-feat-gabito-ballesteros/1896041010</v>
       </c>
       <c r="L122" t="str">
-        <v>minute - Saint Harison</v>
+        <v>Salvame Hoy (feat. Gabito Ballesteros) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>THE LIVING</v>
+        <v>Rubio</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/the-living/1894092345</v>
+        <v>https://music.apple.com/us/song/rubio/6770655339</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-30</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>La Voz Favorita</v>
       </c>
       <c r="G123" t="str">
-        <v>2:48</v>
+        <v>4:42</v>
       </c>
       <c r="H123" t="str">
-        <v>Labrinth</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/the-living/1894092339</v>
+        <v>https://music.apple.com/us/album/rubio/6770654729</v>
       </c>
       <c r="L123" t="str">
-        <v>THE LIVING - Labrinth</v>
+        <v>Rubio - Jay Wheeler</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thug</v>
+        <v>Pary</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thug/6769289966</v>
+        <v>https://music.apple.com/us/song/pary/6767367748</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-30</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thug - Single</v>
+        <v>Con dolor - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>2:52</v>
       </c>
       <c r="H124" t="str">
-        <v>G Herbo</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thug/6769289953</v>
+        <v>https://music.apple.com/us/album/pary/6767367501</v>
       </c>
       <c r="L124" t="str">
-        <v>Thug - G Herbo</v>
+        <v>Pary - Grupo Frontera</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Clap</v>
+        <v>Think As You Drunk</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/clap/6769903711</v>
+        <v>https://music.apple.com/us/song/think-as-you-drunk/6770725979</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-30</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Clap - Single</v>
+        <v>That's Just Me</v>
       </c>
       <c r="G125" t="str">
-        <v>2:04</v>
+        <v>3:48</v>
       </c>
       <c r="H125" t="str">
-        <v>Polo G</v>
+        <v>Riley Green</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/clap/6769903710</v>
+        <v>https://music.apple.com/us/album/think-as-you-drunk/6770725355</v>
       </c>
       <c r="L125" t="str">
-        <v>Clap - Polo G</v>
+        <v>Think As You Drunk - Riley Green</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>GANG BIZNESS</v>
+        <v>Play Your Games</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
+        <v>https://music.apple.com/us/song/play-your-games/6772932837</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-30</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>THE GENTLEMEN'S CLUB</v>
+        <v>Play Your Games - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:47</v>
+        <v>3:15</v>
       </c>
       <c r="H126" t="str">
-        <v>YG</v>
+        <v>Greta Van Fleet</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/greta-van-fleet/646178956</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
+        <v>https://music.apple.com/us/album/play-your-games/6772932835</v>
       </c>
       <c r="L126" t="str">
-        <v>GANG BIZNESS - YG</v>
+        <v>Play Your Games - Greta Van Fleet</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
+        <v>https://music.apple.com/us/song/adjourn-it-feat-serj-tankian-roman-morello/6769340216</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-30</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>A LITTLE VENGEANCE</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H127" t="str">
-        <v>Jessie Reyez</v>
+        <v>Tom Morello</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/tom-morello/466357</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
+        <v>https://music.apple.com/us/album/adjourn-it-feat-serj-tankian-roman-morello/6769340214</v>
       </c>
       <c r="L127" t="str">
-        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
+        <v>Adjourn It (feat. Serj Tankian &amp; Roman Morello) - Tom Morello</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Joshua Tree</v>
+        <v>Essex_Honey.mp3</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
+        <v>https://music.apple.com/us/song/essex-honey-mp3/6771169447</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-30</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
+        <v>Essex_Honey.mp3 - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:50</v>
+        <v>4:49</v>
       </c>
       <c r="H128" t="str">
-        <v>Hans Zimmer</v>
+        <v>Blood Orange</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
+        <v>https://music.apple.com/us/artist/blood-orange/440698865</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
+        <v>https://music.apple.com/us/album/essex-honey-mp3/6771169151</v>
       </c>
       <c r="L128" t="str">
-        <v>Joshua Tree - Hans Zimmer</v>
+        <v>Essex_Honey.mp3 - Blood Orange</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Mi Gran Amor</v>
+        <v>minute</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
+        <v>https://music.apple.com/us/song/minute/1875303122</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-30</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Mi Gran Amor - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G129" t="str">
-        <v>3:37</v>
+        <v>2:59</v>
       </c>
       <c r="H129" t="str">
-        <v>Santana</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/santana/217174</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
+        <v>https://music.apple.com/us/album/minute/1875302904</v>
       </c>
       <c r="L129" t="str">
-        <v>Mi Gran Amor - Santana</v>
+        <v>minute - Saint Harison</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>london</v>
+        <v>THE LIVING</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/london/6770745672</v>
+        <v>https://music.apple.com/us/song/the-living/1894092345</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-30</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>stardust - EP</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>2:48</v>
       </c>
       <c r="H130" t="str">
-        <v>Freya Skye</v>
+        <v>Labrinth</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/london/6770745662</v>
+        <v>https://music.apple.com/us/album/the-living/1894092339</v>
       </c>
       <c r="L130" t="str">
-        <v>london - Freya Skye</v>
+        <v>THE LIVING - Labrinth</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Caution</v>
+        <v>Thug</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/caution/6768487482</v>
+        <v>https://music.apple.com/us/song/thug/6769289966</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-30</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
+        <v>Thug - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:43</v>
+        <v>2:25</v>
       </c>
       <c r="H131" t="str">
-        <v>NMIXX</v>
+        <v>G Herbo</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/g-herbo/1036753321</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/caution/6768487478</v>
+        <v>https://music.apple.com/us/album/thug/6769289953</v>
       </c>
       <c r="L131" t="str">
-        <v>Caution - NMIXX</v>
+        <v>Thug - G Herbo</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>LEMONADE (feat. Becky G)</v>
+        <v>Clap</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
+        <v>https://music.apple.com/us/song/clap/6769903711</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-30</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>LEMONADE - The 2nd Album</v>
+        <v>Clap - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:07</v>
+        <v>2:04</v>
       </c>
       <c r="H132" t="str">
-        <v>aespa</v>
+        <v>Polo G</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/polo-g/1159371412</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
+        <v>https://music.apple.com/us/album/clap/6769903710</v>
       </c>
       <c r="L132" t="str">
-        <v>LEMONADE (feat. Becky G) - aespa</v>
+        <v>Clap - Polo G</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Take Me Back (Leave Me There)</v>
+        <v>GANG BIZNESS</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
+        <v>https://music.apple.com/us/song/gang-bizness/6772383809</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-30</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>THE GENTLEMEN'S CLUB</v>
       </c>
       <c r="G133" t="str">
-        <v>2:58</v>
+        <v>2:47</v>
       </c>
       <c r="H133" t="str">
-        <v>Cody Johnson</v>
+        <v>YG</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
+        <v>https://music.apple.com/us/album/gang-bizness/6772383681</v>
       </c>
       <c r="L133" t="str">
-        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
+        <v>GANG BIZNESS - YG</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Cheap Thrills</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
+        <v>https://music.apple.com/us/song/ur-heartbeat-who-do-u-think-about-at-2am/6765534140</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-30</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Cheap Thrills - Single</v>
+        <v>A LITTLE VENGEANCE</v>
       </c>
       <c r="G134" t="str">
-        <v>2:42</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Gavin Adcock</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
+        <v>https://music.apple.com/us/album/ur-heartbeat-who-do-u-think-about-at-2am/1895983502</v>
       </c>
       <c r="L134" t="str">
-        <v>Cheap Thrills - Gavin Adcock</v>
+        <v>UR HEARTBEAT (WHO DO U THINK ABOUT AT 2AM?) - Jessie Reyez</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ME VALE V</v>
+        <v>Joshua Tree</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
+        <v>https://music.apple.com/us/song/joshua-tree/6771859148</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-30</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>ACOMODO</v>
+        <v>Euphoria: Season 3 (HBO Original Series Soundtrack)</v>
       </c>
       <c r="G135" t="str">
-        <v>3:06</v>
+        <v>2:50</v>
       </c>
       <c r="H135" t="str">
-        <v>Tito Double P</v>
+        <v>Hans Zimmer</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/hans-zimmer/454295032</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
+        <v>https://music.apple.com/us/album/joshua-tree/6771858464</v>
       </c>
       <c r="L135" t="str">
-        <v>ME VALE V - Tito Double P</v>
+        <v>Joshua Tree - Hans Zimmer</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bug In The Cake</v>
+        <v>Mi Gran Amor</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
+        <v>https://music.apple.com/us/song/mi-gran-amor/6773365775</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-30</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Mi Gran Amor - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:48</v>
+        <v>3:37</v>
       </c>
       <c r="H136" t="str">
-        <v>Violet Grohl</v>
+        <v>Santana</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/santana/217174</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
+        <v>https://music.apple.com/us/album/mi-gran-amor/6773365236</v>
       </c>
       <c r="L136" t="str">
-        <v>Bug In The Cake - Violet Grohl</v>
+        <v>Mi Gran Amor - Santana</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Coil</v>
+        <v>london</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/coil/6766858354</v>
+        <v>https://music.apple.com/us/song/london/6770745672</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-30</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Rumspringa</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G137" t="str">
-        <v>3:54</v>
+        <v>3:23</v>
       </c>
       <c r="H137" t="str">
-        <v>ear</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/coil/6766858352</v>
+        <v>https://music.apple.com/us/album/london/6770745662</v>
       </c>
       <c r="L137" t="str">
-        <v>Coil - ear</v>
+        <v>london - Freya Skye</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
+        <v>Caution</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
+        <v>https://music.apple.com/us/song/caution/6768487482</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-30</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
+        <v>K-POPS! (Music from and inspired by K-POPS! Motion Picture)</v>
       </c>
       <c r="G138" t="str">
-        <v>3:30</v>
+        <v>2:43</v>
       </c>
       <c r="H138" t="str">
-        <v>Kneecap</v>
+        <v>NMIXX</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
+        <v>https://music.apple.com/us/album/caution/6768487478</v>
       </c>
       <c r="L138" t="str">
-        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
+        <v>Caution - NMIXX</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Out of my Head</v>
+        <v>LEMONADE (feat. Becky G)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
+        <v>https://music.apple.com/us/song/lemonade-feat-becky-g/1893742425</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-30</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Forgot / Out of my Head - Single</v>
+        <v>LEMONADE - The 2nd Album</v>
       </c>
       <c r="G139" t="str">
-        <v>3:04</v>
+        <v>3:07</v>
       </c>
       <c r="H139" t="str">
-        <v>Cara Delevingne</v>
+        <v>aespa</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
+        <v>https://music.apple.com/us/album/lemonade-feat-becky-g/1893742002</v>
       </c>
       <c r="L139" t="str">
-        <v>Out of my Head - Cara Delevingne</v>
+        <v>LEMONADE (feat. Becky G) - aespa</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Passenger Princess</v>
+        <v>Take Me Back (Leave Me There)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
+        <v>https://music.apple.com/us/song/take-me-back-leave-me-there/1892466278</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-30</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Passenger Princess - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G140" t="str">
-        <v>3:18</v>
+        <v>2:58</v>
       </c>
       <c r="H140" t="str">
-        <v>Perrie</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
+        <v>https://music.apple.com/us/album/take-me-back-leave-me-there/1892465981</v>
       </c>
       <c r="L140" t="str">
-        <v>Passenger Princess - Perrie</v>
+        <v>Take Me Back (Leave Me There) - Cody Johnson</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Man of the House</v>
+        <v>Cheap Thrills</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
+        <v>https://music.apple.com/us/song/cheap-thrills/6771156732</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-30</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>SE9</v>
+        <v>Cheap Thrills - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:35</v>
+        <v>2:42</v>
       </c>
       <c r="H141" t="str">
-        <v>Skye Newman</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
+        <v>https://music.apple.com/us/album/cheap-thrills/6771156723</v>
       </c>
       <c r="L141" t="str">
-        <v>Man of the House - Skye Newman</v>
+        <v>Cheap Thrills - Gavin Adcock</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Beautiful Freeks</v>
+        <v>ME VALE V</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
+        <v>https://music.apple.com/us/song/me-vale-v/6769567844</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-30</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Beautiful Freeks - Single</v>
+        <v>ACOMODO</v>
       </c>
       <c r="G142" t="str">
-        <v>2:37</v>
+        <v>3:06</v>
       </c>
       <c r="H142" t="str">
-        <v>MEEK</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
+        <v>https://music.apple.com/us/album/me-vale-v/6769567568</v>
       </c>
       <c r="L142" t="str">
-        <v>Beautiful Freeks - MEEK</v>
+        <v>ME VALE V - Tito Double P</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
+        <v>Bug In The Cake</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
+        <v>https://music.apple.com/us/song/bug-in-the-cake/1880470542</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-30</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G143" t="str">
-        <v>4:34</v>
+        <v>2:48</v>
       </c>
       <c r="H143" t="str">
-        <v>ILLENIUM</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
+        <v>https://music.apple.com/us/album/bug-in-the-cake/1880470537</v>
       </c>
       <c r="L143" t="str">
-        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
+        <v>Bug In The Cake - Violet Grohl</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Beg For Me (JADE Remix)</v>
+        <v>Coil</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
+        <v>https://music.apple.com/us/song/coil/6766858354</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-30</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Beg For Me (Remix) - Single</v>
+        <v>Rumspringa</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>3:54</v>
       </c>
       <c r="H144" t="str">
-        <v>Lily Allen</v>
+        <v>ear</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
+        <v>https://music.apple.com/us/album/coil/6766858352</v>
       </c>
       <c r="L144" t="str">
-        <v>Beg For Me (JADE Remix) - Lily Allen</v>
+        <v>Coil - ear</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ABOVE IT</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/above-it/6766248703</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars-feat-killer-mike/6769424017</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-30</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>GET THE TABLES - Single</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:45</v>
+        <v>3:30</v>
       </c>
       <c r="H145" t="str">
-        <v>Andy Mineo</v>
+        <v>Kneecap</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/above-it/6766248699</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars-feat-killer-mike/6769423676</v>
       </c>
       <c r="L145" t="str">
-        <v>ABOVE IT - Andy Mineo</v>
+        <v>Smugglers &amp; Scholars (feat. Killer Mike) - Kneecap</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>THE JESUS GENERATION</v>
+        <v>Out of my Head</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
+        <v>https://music.apple.com/us/song/out-of-my-head/6767725166</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-30</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>THE JESUS GENERATION - Single</v>
+        <v>I Forgot / Out of my Head - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:15</v>
+        <v>3:04</v>
       </c>
       <c r="H146" t="str">
-        <v>Forrest Frank</v>
+        <v>Cara Delevingne</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/cara-delevingne/1204798982</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
+        <v>https://music.apple.com/us/album/out-of-my-head/6767725156</v>
       </c>
       <c r="L146" t="str">
-        <v>THE JESUS GENERATION - Forrest Frank</v>
+        <v>Out of my Head - Cara Delevingne</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Is It Over Now?</v>
+        <v>Passenger Princess</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
+        <v>https://music.apple.com/us/song/passenger-princess/6771012228</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-30</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Is It Over Now? - Single</v>
+        <v>Passenger Princess - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:39</v>
+        <v>3:18</v>
       </c>
       <c r="H147" t="str">
-        <v>Elderbrook</v>
+        <v>Perrie</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
+        <v>https://music.apple.com/us/album/passenger-princess/6771012223</v>
       </c>
       <c r="L147" t="str">
-        <v>Is It Over Now? - Elderbrook</v>
+        <v>Passenger Princess - Perrie</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>12 Steps</v>
+        <v>Man of the House</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
+        <v>https://music.apple.com/us/song/man-of-the-house/1893733057</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-30</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>12 Steps - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G148" t="str">
-        <v>3:11</v>
+        <v>2:35</v>
       </c>
       <c r="H148" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
+        <v>https://music.apple.com/us/album/man-of-the-house/1893733056</v>
       </c>
       <c r="L148" t="str">
-        <v>12 Steps - Dexter and The Moonrocks</v>
+        <v>Man of the House - Skye Newman</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Over And Over</v>
+        <v>Beautiful Freeks</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
+        <v>https://music.apple.com/us/song/beautiful-freeks/6764602396</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-30</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>It's A Dying Art</v>
+        <v>Beautiful Freeks - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:38</v>
+        <v>2:37</v>
       </c>
       <c r="H149" t="str">
-        <v>Little Big Town</v>
+        <v>MEEK</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
+        <v>https://music.apple.com/us/album/beautiful-freeks/6764602393</v>
       </c>
       <c r="L149" t="str">
-        <v>Over And Over - Little Big Town</v>
+        <v>Beautiful Freeks - MEEK</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>AMAPOLA</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix]</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/amapola/6769560428</v>
+        <v>https://music.apple.com/us/song/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972616</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-30</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ricky y Mau</v>
+        <v>Slave to the Rithm (I Hate Models Never Alone Remix) [feat. Bring Me The Horizon] - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:22</v>
+        <v>4:34</v>
       </c>
       <c r="H150" t="str">
-        <v>Mau y Ricky</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/amapola/6769559985</v>
+        <v>https://music.apple.com/us/album/slave-to-the-rithm-feat-bring-me-the-horizon-i/6771972613</v>
       </c>
       <c r="L150" t="str">
-        <v>AMAPOLA - Mau y Ricky</v>
+        <v>Slave to the Rithm (feat. Bring Me The Horizon) [I Hate Models Never Alone Remix] - ILLENIUM</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Mad About It</v>
+        <v>Beg For Me (JADE Remix)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
+        <v>https://music.apple.com/us/song/beg-for-me-jade-remix/6771474203</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-30</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mad About It - Single</v>
+        <v>Beg For Me (Remix) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:37</v>
+        <v>2:50</v>
       </c>
       <c r="H151" t="str">
-        <v>Dasha</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
+        <v>https://music.apple.com/us/artist/lily-allen/157063999</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
+        <v>https://music.apple.com/us/album/beg-for-me-jade-remix/6771474201</v>
       </c>
       <c r="L151" t="str">
-        <v>Mad About It - Dasha</v>
+        <v>Beg For Me (JADE Remix) - Lily Allen</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Love’s a Gun</v>
+        <v>ABOVE IT</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
+        <v>https://music.apple.com/us/song/above-it/6766248703</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-30</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Love’s a Gun - Single</v>
+        <v>GET THE TABLES - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:59</v>
+        <v>1:45</v>
       </c>
       <c r="H152" t="str">
-        <v>Daniel Seavey</v>
+        <v>Andy Mineo</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
+        <v>https://music.apple.com/us/artist/andy-mineo/257538441</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
+        <v>https://music.apple.com/us/album/above-it/6766248699</v>
       </c>
       <c r="L152" t="str">
-        <v>Love’s a Gun - Daniel Seavey</v>
+        <v>ABOVE IT - Andy Mineo</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Long Story Short</v>
+        <v>THE JESUS GENERATION</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
+        <v>https://music.apple.com/us/song/the-jesus-generation/6773948895</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-30</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Long Story Short - Single</v>
+        <v>THE JESUS GENERATION - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:48</v>
+        <v>4:15</v>
       </c>
       <c r="H153" t="str">
-        <v>Knox</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
+        <v>https://music.apple.com/us/album/the-jesus-generation/6773948742</v>
       </c>
       <c r="L153" t="str">
-        <v>Long Story Short - Knox</v>
+        <v>THE JESUS GENERATION - Forrest Frank</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>blue jeans</v>
+        <v>Is It Over Now?</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
+        <v>https://music.apple.com/us/song/is-it-over-now/6767564750</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-30</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>blue jeans - Single</v>
+        <v>Is It Over Now? - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>3:39</v>
       </c>
       <c r="H154" t="str">
-        <v>Nightly</v>
+        <v>Elderbrook</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/elderbrook/736829657</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
+        <v>https://music.apple.com/us/album/is-it-over-now/6767564746</v>
       </c>
       <c r="L154" t="str">
-        <v>blue jeans - Nightly</v>
+        <v>Is It Over Now? - Elderbrook</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Que Gacho</v>
+        <v>12 Steps</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
+        <v>https://music.apple.com/us/song/12-steps/6769559623</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-30</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Que Gacho - Single</v>
+        <v>12 Steps - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:13</v>
+        <v>3:11</v>
       </c>
       <c r="H155" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
+        <v>https://music.apple.com/us/album/12-steps/6769559618</v>
       </c>
       <c r="L155" t="str">
-        <v>Que Gacho - Luis R Conriquez</v>
+        <v>12 Steps - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>same God</v>
+        <v>Over And Over</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/same-god/1878232616</v>
+        <v>https://music.apple.com/us/song/over-and-over/6771585908</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-30</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>It's A Dying Art</v>
       </c>
       <c r="G156" t="str">
-        <v>3:34</v>
+        <v>4:38</v>
       </c>
       <c r="H156" t="str">
-        <v>Alana Springsteen</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/little-big-town/513770</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/same-god/1878232194</v>
+        <v>https://music.apple.com/us/album/over-and-over/6771585889</v>
       </c>
       <c r="L156" t="str">
-        <v>same God - Alana Springsteen</v>
+        <v>Over And Over - Little Big Town</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>emotional swaggage</v>
+        <v>AMAPOLA</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
+        <v>https://music.apple.com/us/song/amapola/6769560428</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-30</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>IDCASH</v>
+        <v>Ricky y Mau</v>
       </c>
       <c r="G157" t="str">
-        <v>2:12</v>
+        <v>2:22</v>
       </c>
       <c r="H157" t="str">
-        <v>IDK</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/idk/1578186947</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
+        <v>https://music.apple.com/us/album/amapola/6769559985</v>
       </c>
       <c r="L157" t="str">
-        <v>emotional swaggage - IDK</v>
+        <v>AMAPOLA - Mau y Ricky</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Baby Driver</v>
+        <v>Mad About It</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
+        <v>https://music.apple.com/us/song/mad-about-it/6767425272</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-30</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Baby Driver - Single</v>
+        <v>Mad About It - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>2:37</v>
       </c>
       <c r="H158" t="str">
-        <v>070 Shake</v>
+        <v>Dasha</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
+        <v>https://music.apple.com/us/artist/dasha/1462663731</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
+        <v>https://music.apple.com/us/album/mad-about-it/6767425271</v>
       </c>
       <c r="L158" t="str">
-        <v>Baby Driver - 070 Shake</v>
+        <v>Mad About It - Dasha</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>More! More! More!</v>
+        <v>Love’s a Gun</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
+        <v>https://music.apple.com/us/song/loves-a-gun/6771898253</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-30</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>REBECCA</v>
+        <v>Love’s a Gun - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:55</v>
+        <v>2:59</v>
       </c>
       <c r="H159" t="str">
-        <v>Becky Hill</v>
+        <v>Daniel Seavey</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/daniel-seavey/1646124302</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
+        <v>https://music.apple.com/us/album/loves-a-gun/6771897951</v>
       </c>
       <c r="L159" t="str">
-        <v>More! More! More! - Becky Hill</v>
+        <v>Love’s a Gun - Daniel Seavey</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Young Again</v>
+        <v>Long Story Short</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/young-again/1877229743</v>
+        <v>https://music.apple.com/us/song/long-story-short/6770700866</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-30</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>EI8HT</v>
+        <v>Long Story Short - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:36</v>
+        <v>2:48</v>
       </c>
       <c r="H160" t="str">
-        <v>Shinedown</v>
+        <v>Knox</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/young-again/1877229738</v>
+        <v>https://music.apple.com/us/album/long-story-short/6770700853</v>
       </c>
       <c r="L160" t="str">
-        <v>Young Again - Shinedown</v>
+        <v>Long Story Short - Knox</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>skinny dip</v>
+        <v>blue jeans</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
+        <v>https://music.apple.com/us/song/blue-jeans/6770529591</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-30</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>skinny dip - Single</v>
+        <v>blue jeans - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:12</v>
+        <v>2:37</v>
       </c>
       <c r="H161" t="str">
-        <v>almost monday</v>
+        <v>Nightly</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
+        <v>https://music.apple.com/us/album/blue-jeans/6770529589</v>
       </c>
       <c r="L161" t="str">
-        <v>skinny dip - almost monday</v>
+        <v>blue jeans - Nightly</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>girls like girls (from the motion picture)</v>
+        <v>Que Gacho</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
+        <v>https://music.apple.com/us/song/que-gacho/6770628420</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-30</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>girls like girls the album</v>
+        <v>Que Gacho - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:14</v>
+        <v>3:13</v>
       </c>
       <c r="H162" t="str">
-        <v>Hayley Kiyoko</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
+        <v>https://music.apple.com/us/album/que-gacho/6770628419</v>
       </c>
       <c r="L162" t="str">
-        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
+        <v>Que Gacho - Luis R Conriquez</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Better Off</v>
+        <v>same God</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/better-off/6772045367</v>
+        <v>https://music.apple.com/us/song/same-god/1878232616</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-30</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Stages</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G163" t="str">
-        <v>3:16</v>
+        <v>3:34</v>
       </c>
       <c r="H163" t="str">
-        <v>Lauren Alaina</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/better-off/6772044978</v>
+        <v>https://music.apple.com/us/album/same-god/1878232194</v>
       </c>
       <c r="L163" t="str">
-        <v>Better Off - Lauren Alaina</v>
+        <v>same God - Alana Springsteen</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
+        <v>emotional swaggage</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
+        <v>https://music.apple.com/us/song/emotional-swaggage/6767397453</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-30</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
+        <v>IDCASH</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>2:12</v>
       </c>
       <c r="H164" t="str">
-        <v>Monaleo</v>
+        <v>IDK</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
+        <v>https://music.apple.com/us/artist/idk/1578186947</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
+        <v>https://music.apple.com/us/album/emotional-swaggage/6767397348</v>
       </c>
       <c r="L164" t="str">
-        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
+        <v>emotional swaggage - IDK</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Lost in translation...</v>
+        <v>Baby Driver</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
+        <v>https://music.apple.com/us/song/baby-driver/6769152279</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-30</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Baby Driver - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:30</v>
+        <v>3:36</v>
       </c>
       <c r="H165" t="str">
-        <v>R3HAB</v>
+        <v>070 Shake</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/070-shake/1097177293</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
+        <v>https://music.apple.com/us/album/baby-driver/6769152273</v>
       </c>
       <c r="L165" t="str">
-        <v>Lost in translation... - R3HAB</v>
+        <v>Baby Driver - 070 Shake</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Call Security</v>
+        <v>More! More! More!</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/call-security/6769296603</v>
+        <v>https://music.apple.com/us/song/more-more-more/6770600105</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-30</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>U, Me &amp; My Ego</v>
+        <v>REBECCA</v>
       </c>
       <c r="G166" t="str">
-        <v>3:22</v>
+        <v>2:55</v>
       </c>
       <c r="H166" t="str">
-        <v>Chxrry</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/call-security/6769296591</v>
+        <v>https://music.apple.com/us/album/more-more-more/6770600098</v>
       </c>
       <c r="L166" t="str">
-        <v>Call Security - Chxrry</v>
+        <v>More! More! More! - Becky Hill</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>chaotic</v>
+        <v>Young Again</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
+        <v>https://music.apple.com/us/song/young-again/1877229743</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-30</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>scars to prove it</v>
+        <v>EI8HT</v>
       </c>
       <c r="G167" t="str">
-        <v>3:14</v>
+        <v>3:36</v>
       </c>
       <c r="H167" t="str">
-        <v>Hailey Picardi</v>
+        <v>Shinedown</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
+        <v>https://music.apple.com/us/album/young-again/1877229738</v>
       </c>
       <c r="L167" t="str">
-        <v>chaotic - Hailey Picardi</v>
+        <v>Young Again - Shinedown</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Keep It To Yourself</v>
+        <v>skinny dip</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
+        <v>https://music.apple.com/us/song/skinny-dip/6769856281</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-30</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>LOVE IS THE LAW</v>
+        <v>skinny dip - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:17</v>
+        <v>3:12</v>
       </c>
       <c r="H168" t="str">
-        <v>Love Spells</v>
+        <v>almost monday</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
+        <v>https://music.apple.com/us/album/skinny-dip/6769855907</v>
       </c>
       <c r="L168" t="str">
-        <v>Keep It To Yourself - Love Spells</v>
+        <v>skinny dip - almost monday</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Something to Someone</v>
+        <v>girls like girls (from the motion picture)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
+        <v>https://music.apple.com/us/song/girls-like-girls-from-the-motion-picture/1893704575</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-30</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Something to Someone - Single</v>
+        <v>girls like girls the album</v>
       </c>
       <c r="G169" t="str">
-        <v>3:55</v>
+        <v>4:14</v>
       </c>
       <c r="H169" t="str">
-        <v>Max McNown</v>
+        <v>Hayley Kiyoko</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/hayley-kiyoko/325569584</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
+        <v>https://music.apple.com/us/album/girls-like-girls-from-the-motion-picture/1893704396</v>
       </c>
       <c r="L169" t="str">
-        <v>Something to Someone - Max McNown</v>
+        <v>girls like girls (from the motion picture) - Hayley Kiyoko</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Green Screen (1pm)</v>
+        <v>Better Off</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
+        <v>https://music.apple.com/us/song/better-off/6772045367</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-30</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Hours: High Noon</v>
+        <v>Stages</v>
       </c>
       <c r="G170" t="str">
-        <v>2:10</v>
+        <v>3:16</v>
       </c>
       <c r="H170" t="str">
-        <v>Cautious Clay</v>
+        <v>Lauren Alaina</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
+        <v>https://music.apple.com/us/artist/lauren-alaina/425028816</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
+        <v>https://music.apple.com/us/album/better-off/6772044978</v>
       </c>
       <c r="L170" t="str">
-        <v>Green Screen (1pm) - Cautious Clay</v>
+        <v>Better Off - Lauren Alaina</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Scoreboard</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
+        <v>https://music.apple.com/us/song/everythang-pinka-feat-teezo-touchdown/6772026590</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-30</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>I Just Wanna Be Loved</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:24</v>
+        <v>2:48</v>
       </c>
       <c r="H171" t="str">
-        <v>Gabriella Rose</v>
+        <v>Monaleo</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/monaleo/1495603374</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
+        <v>https://music.apple.com/us/album/everythang-pinka-feat-teezo-touchdown/6772026586</v>
       </c>
       <c r="L171" t="str">
-        <v>Scoreboard - Gabriella Rose</v>
+        <v>Everythang Pinka (feat. Teezo Touchdown) - Monaleo</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>High</v>
+        <v>Lost in translation...</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/high/6773775211</v>
+        <v>https://music.apple.com/us/song/lost-in-translation/1870971556</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-30</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Payback Is A Dog (EP)</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:30</v>
       </c>
       <c r="H172" t="str">
-        <v>Nia Smith</v>
+        <v>R3HAB</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/high/6773775203</v>
+        <v>https://music.apple.com/us/album/lost-in-translation/1870971550</v>
       </c>
       <c r="L172" t="str">
-        <v>High - Nia Smith</v>
+        <v>Lost in translation... - R3HAB</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Ay Gyal</v>
+        <v>Call Security</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/ay-gyal/6771885805</v>
+        <v>https://music.apple.com/us/song/call-security/6769296603</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-30</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Ay Gyal - Single</v>
+        <v>U, Me &amp; My Ego</v>
       </c>
       <c r="G173" t="str">
-        <v>2:12</v>
+        <v>3:22</v>
       </c>
       <c r="H173" t="str">
-        <v>1Ski OG</v>
+        <v>Chxrry</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/ay-gyal/6771885803</v>
+        <v>https://music.apple.com/us/album/call-security/6769296591</v>
       </c>
       <c r="L173" t="str">
-        <v>Ay Gyal - 1Ski OG</v>
+        <v>Call Security - Chxrry</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>always knew</v>
+        <v>chaotic</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/always-knew/6762864274</v>
+        <v>https://music.apple.com/us/song/chaotic/6767629281</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-30</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>always knew - Single</v>
+        <v>scars to prove it</v>
       </c>
       <c r="G174" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H174" t="str">
-        <v>Biscits</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/biscits/1185553226</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/always-knew/1895047928</v>
+        <v>https://music.apple.com/us/album/chaotic/6767626506</v>
       </c>
       <c r="L174" t="str">
-        <v>always knew - Biscits</v>
+        <v>chaotic - Hailey Picardi</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Cigarette Burns</v>
+        <v>Keep It To Yourself</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cigarette-burns/6770691000</v>
+        <v>https://music.apple.com/us/song/keep-it-to-yourself/6771099675</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-30</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Heartland Rock and Roll</v>
+        <v>LOVE IS THE LAW</v>
       </c>
       <c r="G175" t="str">
-        <v>2:41</v>
+        <v>4:17</v>
       </c>
       <c r="H175" t="str">
-        <v>Corey Kent</v>
+        <v>Love Spells</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cigarette-burns/6770690867</v>
+        <v>https://music.apple.com/us/album/keep-it-to-yourself/6771099661</v>
       </c>
       <c r="L175" t="str">
-        <v>Cigarette Burns - Corey Kent</v>
+        <v>Keep It To Yourself - Love Spells</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Let You Down</v>
+        <v>Something to Someone</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/let-you-down/6773362320</v>
+        <v>https://music.apple.com/us/song/something-to-someone/6767255424</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-30</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>El Relevo</v>
+        <v>Something to Someone - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:14</v>
+        <v>3:55</v>
       </c>
       <c r="H176" t="str">
-        <v>Luis Figueroa</v>
+        <v>Max McNown</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/luis-figueroa/395266944</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/let-you-down/6773362108</v>
+        <v>https://music.apple.com/us/album/something-to-someone/1896445136</v>
       </c>
       <c r="L176" t="str">
-        <v>Let You Down - Luis Figueroa</v>
+        <v>Something to Someone - Max McNown</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Starless</v>
+        <v>Green Screen (1pm)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/starless/6770568779</v>
+        <v>https://music.apple.com/us/song/green-screen-1pm/6766279426</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-30</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Starless - Single</v>
+        <v>The Hours: High Noon</v>
       </c>
       <c r="G177" t="str">
-        <v>4:32</v>
+        <v>2:10</v>
       </c>
       <c r="H177" t="str">
-        <v>A Perfect Circle</v>
+        <v>Cautious Clay</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/a-perfect-circle/652503</v>
+        <v>https://music.apple.com/us/artist/cautious-clay/1064628701</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/starless/6770568776</v>
+        <v>https://music.apple.com/us/album/green-screen-1pm/1896264236</v>
       </c>
       <c r="L177" t="str">
-        <v>Starless - A Perfect Circle</v>
+        <v>Green Screen (1pm) - Cautious Clay</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Looking For You</v>
+        <v>Scoreboard</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/looking-for-you/6768355609</v>
+        <v>https://music.apple.com/us/song/scoreboard/6767255746</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-30</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Looking For You - Single</v>
+        <v>I Just Wanna Be Loved</v>
       </c>
       <c r="G178" t="str">
-        <v>3:19</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>Gable Price and Friends</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gable-price-and-friends/1441378212</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/looking-for-you/6768355596</v>
+        <v>https://music.apple.com/us/album/scoreboard/1896445371</v>
       </c>
       <c r="L178" t="str">
-        <v>Looking For You - Gable Price and Friends</v>
+        <v>Scoreboard - Gabriella Rose</v>
       </c>
     </row